--- a/Test Execution Report/Feature Reports/Dashboard.xlsx
+++ b/Test Execution Report/Feature Reports/Dashboard.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O28"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="45.83203125" customWidth="1"/>
@@ -504,7 +504,7 @@
         <v>Automation (Playwright)</v>
       </c>
       <c r="M2" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N2" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Automation (Playwright)</v>
       </c>
       <c r="M3" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N3" t="str">
         <v>BUG-DASHBOARD-002</v>
@@ -602,7 +602,7 @@
         <v>Automation (Playwright)</v>
       </c>
       <c r="M4" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N4" t="str">
         <v/>
@@ -651,7 +651,7 @@
         <v>Automation (Playwright)</v>
       </c>
       <c r="M5" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N5" t="str">
         <v>BUG-DASHBOARD-004</v>
@@ -700,7 +700,7 @@
         <v>Automation (Playwright)</v>
       </c>
       <c r="M6" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N6" t="str">
         <v>BUG-DASHBOARD-005</v>
@@ -749,7 +749,7 @@
         <v>Automation (Playwright)</v>
       </c>
       <c r="M7" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N7" t="str">
         <v/>
@@ -798,7 +798,7 @@
         <v>Automation (Playwright)</v>
       </c>
       <c r="M8" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N8" t="str">
         <v>BUG-DASHBOARD-007</v>
@@ -847,7 +847,7 @@
         <v>Automation (Playwright)</v>
       </c>
       <c r="M9" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N9" t="str">
         <v/>
@@ -896,7 +896,7 @@
         <v>Automation (Playwright)</v>
       </c>
       <c r="M10" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N10" t="str">
         <v/>
@@ -945,7 +945,7 @@
         <v>Automation (Playwright)</v>
       </c>
       <c r="M11" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N11" t="str">
         <v/>
@@ -994,7 +994,7 @@
         <v>Automation (Playwright)</v>
       </c>
       <c r="M12" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N12" t="str">
         <v>BUG-DASHBOARD-011</v>
@@ -1043,7 +1043,7 @@
         <v>Automation (Playwright)</v>
       </c>
       <c r="M13" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N13" t="str">
         <v/>
@@ -1092,7 +1092,7 @@
         <v>Automation (Playwright)</v>
       </c>
       <c r="M14" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N14" t="str">
         <v/>
@@ -1141,7 +1141,7 @@
         <v>Automation (Playwright)</v>
       </c>
       <c r="M15" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N15" t="str">
         <v/>
@@ -1190,18 +1190,606 @@
         <v>Automation (Playwright)</v>
       </c>
       <c r="M16" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N16" t="str">
         <v/>
       </c>
       <c r="O16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>TC-LOGIN-001</v>
+      </c>
+      <c r="B17" t="str">
+        <v>TC-LOGIN-001 | Login page loads with all UI elements</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D17" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G17" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M17" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>TC-LOGIN-002</v>
+      </c>
+      <c r="B18" t="str">
+        <v>TC-LOGIN-002 | Valid credentials redirect to dashboard</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G18" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M18" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>TC-LOGIN-003</v>
+      </c>
+      <c r="B19" t="str">
+        <v>TC-LOGIN-003 | Login with Remember Me checked</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G19" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M19" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>TC-LOGIN-004</v>
+      </c>
+      <c r="B20" t="str">
+        <v>TC-LOGIN-004 | Invalid username shows error</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E20" t="str">
+        <v>High</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G20" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M20" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>TC-LOGIN-005</v>
+      </c>
+      <c r="B21" t="str">
+        <v>TC-LOGIN-005 | Invalid password shows error</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E21" t="str">
+        <v>High</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G21" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M21" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>TC-LOGIN-006</v>
+      </c>
+      <c r="B22" t="str">
+        <v>TC-LOGIN-006 | Empty username blocked</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E22" t="str">
+        <v>High</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G22" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M22" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>TC-LOGIN-007</v>
+      </c>
+      <c r="B23" t="str">
+        <v>TC-LOGIN-007 | Empty password blocked</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E23" t="str">
+        <v>High</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G23" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K23" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M23" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>TC-LOGIN-008</v>
+      </c>
+      <c r="B24" t="str">
+        <v>TC-LOGIN-008 | Both fields empty blocked</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E24" t="str">
+        <v>High</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G24" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K24" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M24" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>TC-LOGIN-009</v>
+      </c>
+      <c r="B25" t="str">
+        <v>TC-LOGIN-009 | SQL injection rejected</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E25" t="str">
+        <v>High</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G25" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J25" t="str">
+        <v>_x001b_[31mTest timeout of 30000ms exceeded._x001b_[39m</v>
+      </c>
+      <c r="K25" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M25" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>TC-LOGIN-010</v>
+      </c>
+      <c r="B26" t="str">
+        <v>TC-LOGIN-010 | XSS payload rejected</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E26" t="str">
+        <v>High</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G26" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K26" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M26" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>TC-LOGIN-011</v>
+      </c>
+      <c r="B27" t="str">
+        <v>TC-LOGIN-011 | Max length username (256 chars) handled</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G27" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K27" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M27" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>TC-LOGIN-012</v>
+      </c>
+      <c r="B28" t="str">
+        <v>TC-LOGIN-012 | Password field masks input</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D28" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G28" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K28" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M28" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O28"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1315,7 +1903,7 @@
         <v>New</v>
       </c>
       <c r="L2" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -1367,7 +1955,7 @@
         <v>New</v>
       </c>
       <c r="L3" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -1419,7 +2007,7 @@
         <v>New</v>
       </c>
       <c r="L4" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -1471,7 +2059,7 @@
         <v>New</v>
       </c>
       <c r="L5" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -1523,7 +2111,7 @@
         <v>New</v>
       </c>
       <c r="L6" t="str">
-        <v>24 Jun 2026</v>
+        <v>25 Jun 2026</v>
       </c>
       <c r="M6" t="str">
         <v/>

--- a/Test Execution Report/Feature Reports/Dashboard.xlsx
+++ b/Test Execution Report/Feature Reports/Dashboard.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O48"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="45.83203125" customWidth="1"/>
@@ -466,10 +466,10 @@
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>TC-DASH-001</v>
+        <v>TC-TICKET-001</v>
       </c>
       <c r="B2" t="str">
-        <v>TC-DASH-001 | Dashboard page loads with title and H1</v>
+        <v>TC-TICKET-001 | Create Ticket page loads with all required fields</v>
       </c>
       <c r="C2" t="str">
         <v>Dashboard</v>
@@ -515,10 +515,10 @@
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>TC-DASH-002</v>
+        <v>TC-TICKET-002</v>
       </c>
       <c r="B3" t="str">
-        <v>TC-DASH-002 | All 4 stat cards visible with values</v>
+        <v>TC-TICKET-002 | Submit ticket with all required fields filled</v>
       </c>
       <c r="C3" t="str">
         <v>Dashboard</v>
@@ -544,10 +544,10 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J3" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+        <v>Test passed successfully</v>
       </c>
       <c r="K3" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L3" t="str">
         <v>Automation (Playwright)</v>
@@ -556,7 +556,7 @@
         <v>25 Jun 2026</v>
       </c>
       <c r="N3" t="str">
-        <v>BUG-DASHBOARD-002</v>
+        <v/>
       </c>
       <c r="O3" t="str">
         <v/>
@@ -564,16 +564,16 @@
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>TC-DASH-003</v>
+        <v>TC-TICKET-003</v>
       </c>
       <c r="B4" t="str">
-        <v>TC-DASH-003 | OVERVIEW and ANALYTICS buttons visible</v>
+        <v>TC-TICKET-003 | Project dropdown shows all available projects</v>
       </c>
       <c r="C4" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D4" t="str">
-        <v>UI</v>
+        <v>Positive</v>
       </c>
       <c r="E4" t="str">
         <v>Low</v>
@@ -613,10 +613,10 @@
     </row>
     <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>TC-DASH-004</v>
+        <v>TC-TICKET-004</v>
       </c>
       <c r="B5" t="str">
-        <v>TC-DASH-004 | ANALYTICS tab shows analytics content</v>
+        <v>TC-TICKET-004 | Selecting project unlocks Platform dropdown</v>
       </c>
       <c r="C5" t="str">
         <v>Dashboard</v>
@@ -642,10 +642,10 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J5" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+        <v>Test passed successfully</v>
       </c>
       <c r="K5" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L5" t="str">
         <v>Automation (Playwright)</v>
@@ -654,7 +654,7 @@
         <v>25 Jun 2026</v>
       </c>
       <c r="N5" t="str">
-        <v>BUG-DASHBOARD-004</v>
+        <v/>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -662,16 +662,16 @@
     </row>
     <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>TC-DASH-005</v>
+        <v>TC-TICKET-005</v>
       </c>
       <c r="B6" t="str">
-        <v>TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
+        <v>TC-TICKET-005 | All Ticket Type chips are visible</v>
       </c>
       <c r="C6" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D6" t="str">
-        <v>Positive</v>
+        <v>UI</v>
       </c>
       <c r="E6" t="str">
         <v>Low</v>
@@ -691,7 +691,7 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J6" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+        <v xml:space="preserve">Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('text=SCR').first() Expected: visible Received: hidden Timeout:  5000ms  Call log: _x001b_[2m  - </v>
       </c>
       <c r="K6" t="str">
         <v>FAIL</v>
@@ -711,10 +711,10 @@
     </row>
     <row r="7" xml:space="preserve">
       <c r="A7" t="str">
-        <v>TC-DASH-006</v>
+        <v>TC-TICKET-006</v>
       </c>
       <c r="B7" t="str">
-        <v>TC-DASH-006 | Date range filter applies correctly</v>
+        <v>TC-TICKET-006 | Description character counter updates on input</v>
       </c>
       <c r="C7" t="str">
         <v>Dashboard</v>
@@ -740,10 +740,10 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J7" t="str">
-        <v>Test passed successfully</v>
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mnot_x001b_[2m._x001b_[22mtoBe_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m) // Object.is equality_x001b_[22m  Expected: not _x001b_[32m"0 / 2000"_x001b_[39m</v>
       </c>
       <c r="K7" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="L7" t="str">
         <v>Automation (Playwright)</v>
@@ -752,7 +752,7 @@
         <v>25 Jun 2026</v>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>BUG-DASHBOARD-006</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -760,10 +760,10 @@
     </row>
     <row r="8" xml:space="preserve">
       <c r="A8" t="str">
-        <v>TC-DASH-007</v>
+        <v>TC-TICKET-007</v>
       </c>
       <c r="B8" t="str">
-        <v>TC-DASH-007 | Reset button clears date filter</v>
+        <v>TC-TICKET-007 | Reset button clears all filled fields</v>
       </c>
       <c r="C8" t="str">
         <v>Dashboard</v>
@@ -789,7 +789,7 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J8" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('button:has-text("Reset")').first() Expected: visible Received: hidden Timeout:  5000ms  Ca</v>
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBe_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m) // Object.is equality_x001b_[22m  Expected: _x001b_[32m""_x001b_[39m Received: _x001b_[31m"Some description text here"_x001b_[39m</v>
       </c>
       <c r="K8" t="str">
         <v>FAIL</v>
@@ -809,19 +809,19 @@
     </row>
     <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>TC-DASH-008</v>
+        <v>TC-TICKET-008</v>
       </c>
       <c r="B9" t="str">
-        <v>TC-DASH-008 | Invalid date range To &lt; From handled gracefully</v>
+        <v>TC-TICKET-008 | Page/Screen Name field is optional</v>
       </c>
       <c r="C9" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D9" t="str">
-        <v>Negative</v>
+        <v>Positive</v>
       </c>
       <c r="E9" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="F9" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online</v>
@@ -858,10 +858,10 @@
     </row>
     <row r="10" xml:space="preserve">
       <c r="A10" t="str">
-        <v>TC-DASH-009</v>
+        <v>TC-TICKET-009</v>
       </c>
       <c r="B10" t="str">
-        <v>TC-DASH-009 | Active Tickets table with correct columns</v>
+        <v>TC-TICKET-009 | Submit with no fields filled shows validation popup</v>
       </c>
       <c r="C10" t="str">
         <v>Dashboard</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="11" xml:space="preserve">
       <c r="A11" t="str">
-        <v>TC-DASH-010</v>
+        <v>TC-TICKET-010</v>
       </c>
       <c r="B11" t="str">
-        <v>TC-DASH-010 | View All link navigates to ticket list</v>
+        <v>TC-TICKET-010 | Submit without Project shows Missing Information</v>
       </c>
       <c r="C11" t="str">
         <v>Dashboard</v>
@@ -956,10 +956,10 @@
     </row>
     <row r="12" xml:space="preserve">
       <c r="A12" t="str">
-        <v>TC-DASH-011</v>
+        <v>TC-TICKET-011</v>
       </c>
       <c r="B12" t="str">
-        <v>TC-DASH-011 | All sidebar navigation links present</v>
+        <v>TC-TICKET-011 | Submit without Ticket Type shows validation error</v>
       </c>
       <c r="C12" t="str">
         <v>Dashboard</v>
@@ -985,10 +985,10 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J12" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout:  5000ms  Cal</v>
+        <v>Test passed successfully</v>
       </c>
       <c r="K12" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L12" t="str">
         <v>Automation (Playwright)</v>
@@ -997,7 +997,7 @@
         <v>25 Jun 2026</v>
       </c>
       <c r="N12" t="str">
-        <v>BUG-DASHBOARD-011</v>
+        <v/>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="13" xml:space="preserve">
       <c r="A13" t="str">
-        <v>TC-DASH-012</v>
+        <v>TC-TICKET-012</v>
       </c>
       <c r="B13" t="str">
-        <v>TC-DASH-012 | Action Queue badge shows ticket count</v>
+        <v>TC-TICKET-012 | Submit without Description shows validation error</v>
       </c>
       <c r="C13" t="str">
         <v>Dashboard</v>
@@ -1054,10 +1054,10 @@
     </row>
     <row r="14" xml:space="preserve">
       <c r="A14" t="str">
-        <v>TC-DASH-013</v>
+        <v>TC-TICKET-013</v>
       </c>
       <c r="B14" t="str">
-        <v>TC-DASH-013 | Search box accepts input</v>
+        <v>TC-TICKET-013 | Submit without Platform shows validation error</v>
       </c>
       <c r="C14" t="str">
         <v>Dashboard</v>
@@ -1103,16 +1103,16 @@
     </row>
     <row r="15" xml:space="preserve">
       <c r="A15" t="str">
-        <v>TC-DASH-014</v>
+        <v>TC-TICKET-014</v>
       </c>
       <c r="B15" t="str">
-        <v>TC-DASH-014 | User profile dropdown shows username and links</v>
+        <v>TC-TICKET-014 | Description with exactly 14 chars fails validation</v>
       </c>
       <c r="C15" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D15" t="str">
-        <v>Positive</v>
+        <v>Negative</v>
       </c>
       <c r="E15" t="str">
         <v>Low</v>
@@ -1132,10 +1132,10 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J15" t="str">
-        <v>Test passed successfully</v>
+        <v xml:space="preserve">Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoMatch_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m)_x001b_[22m  Expected pattern: _x001b_[32m/Description/i_x001b_[39m Received string:  _x001b_[31m"Are you sure you want to log this </v>
       </c>
       <c r="K15" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="L15" t="str">
         <v>Automation (Playwright)</v>
@@ -1144,7 +1144,7 @@
         <v>25 Jun 2026</v>
       </c>
       <c r="N15" t="str">
-        <v/>
+        <v>BUG-DASHBOARD-014</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -1152,10 +1152,10 @@
     </row>
     <row r="16" xml:space="preserve">
       <c r="A16" t="str">
-        <v>TC-DASH-015</v>
+        <v>TC-TICKET-015</v>
       </c>
       <c r="B16" t="str">
-        <v>TC-DASH-015 | Dashboard inaccessible without login</v>
+        <v>TC-TICKET-015 | Description with exactly 15 chars passes validation</v>
       </c>
       <c r="C16" t="str">
         <v>Dashboard</v>
@@ -1201,19 +1201,19 @@
     </row>
     <row r="17" xml:space="preserve">
       <c r="A17" t="str">
-        <v>TC-LOGIN-001</v>
+        <v>TC-TICKET-016</v>
       </c>
       <c r="B17" t="str">
-        <v>TC-LOGIN-001 | Login page loads with all UI elements</v>
+        <v>TC-TICKET-016 | Description at 2000 chars (max) is accepted</v>
       </c>
       <c r="C17" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D17" t="str">
-        <v>UI</v>
+        <v>Boundary</v>
       </c>
       <c r="E17" t="str">
-        <v>Critical</v>
+        <v>Medium</v>
       </c>
       <c r="F17" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online</v>
@@ -1230,10 +1230,10 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J17" t="str">
-        <v>Test passed successfully</v>
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBe_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m) // Object.is equality_x001b_[22m  Expected: _x001b_[32m2000_x001b_[39m Received: _x001b_[31m0_x001b_[39m</v>
       </c>
       <c r="K17" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="L17" t="str">
         <v>Automation (Playwright)</v>
@@ -1242,7 +1242,7 @@
         <v>25 Jun 2026</v>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>BUG-DASHBOARD-016</v>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="18" xml:space="preserve">
       <c r="A18" t="str">
-        <v>TC-LOGIN-002</v>
+        <v>TC-TICKET-017</v>
       </c>
       <c r="B18" t="str">
-        <v>TC-LOGIN-002 | Valid credentials redirect to dashboard</v>
+        <v>TC-TICKET-017 | Platform chips show all expected options after project selected</v>
       </c>
       <c r="C18" t="str">
         <v>Dashboard</v>
@@ -1299,19 +1299,19 @@
     </row>
     <row r="19" xml:space="preserve">
       <c r="A19" t="str">
-        <v>TC-LOGIN-003</v>
+        <v>TC-TICKET-018</v>
       </c>
       <c r="B19" t="str">
-        <v>TC-LOGIN-003 | Login with Remember Me checked</v>
+        <v>TC-TICKET-018 | SQL injection in description is handled safely</v>
       </c>
       <c r="C19" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D19" t="str">
-        <v>Positive</v>
+        <v>Security</v>
       </c>
       <c r="E19" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="F19" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online</v>
@@ -1348,16 +1348,16 @@
     </row>
     <row r="20" xml:space="preserve">
       <c r="A20" t="str">
-        <v>TC-LOGIN-004</v>
+        <v>TC-TICKET-019</v>
       </c>
       <c r="B20" t="str">
-        <v>TC-LOGIN-004 | Invalid username shows error</v>
+        <v>TC-TICKET-019 | XSS payload in description is handled safely</v>
       </c>
       <c r="C20" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D20" t="str">
-        <v>Negative</v>
+        <v>Security</v>
       </c>
       <c r="E20" t="str">
         <v>High</v>
@@ -1397,19 +1397,19 @@
     </row>
     <row r="21" xml:space="preserve">
       <c r="A21" t="str">
-        <v>TC-LOGIN-005</v>
+        <v>TC-TICKET-020</v>
       </c>
       <c r="B21" t="str">
-        <v>TC-LOGIN-005 | Invalid password shows error</v>
+        <v>TC-TICKET-020 | Unauthenticated user is redirected to login page</v>
       </c>
       <c r="C21" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D21" t="str">
-        <v>Negative</v>
+        <v>Positive</v>
       </c>
       <c r="E21" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="F21" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online</v>
@@ -1446,19 +1446,19 @@
     </row>
     <row r="22" xml:space="preserve">
       <c r="A22" t="str">
-        <v>TC-LOGIN-006</v>
+        <v>TC-DASH-001</v>
       </c>
       <c r="B22" t="str">
-        <v>TC-LOGIN-006 | Empty username blocked</v>
+        <v>TC-DASH-001 | Dashboard page loads with title and H1</v>
       </c>
       <c r="C22" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D22" t="str">
-        <v>Boundary</v>
+        <v>UI</v>
       </c>
       <c r="E22" t="str">
-        <v>High</v>
+        <v>Critical</v>
       </c>
       <c r="F22" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online</v>
@@ -1495,19 +1495,19 @@
     </row>
     <row r="23" xml:space="preserve">
       <c r="A23" t="str">
-        <v>TC-LOGIN-007</v>
+        <v>TC-DASH-002</v>
       </c>
       <c r="B23" t="str">
-        <v>TC-LOGIN-007 | Empty password blocked</v>
+        <v>TC-DASH-002 | All 4 stat cards visible with values</v>
       </c>
       <c r="C23" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D23" t="str">
-        <v>Boundary</v>
+        <v>UI</v>
       </c>
       <c r="E23" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="F23" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online</v>
@@ -1524,10 +1524,10 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J23" t="str">
-        <v>Test passed successfully</v>
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
       </c>
       <c r="K23" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="L23" t="str">
         <v>Automation (Playwright)</v>
@@ -1536,7 +1536,7 @@
         <v>25 Jun 2026</v>
       </c>
       <c r="N23" t="str">
-        <v/>
+        <v>BUG-DASHBOARD-022</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -1544,19 +1544,19 @@
     </row>
     <row r="24" xml:space="preserve">
       <c r="A24" t="str">
-        <v>TC-LOGIN-008</v>
+        <v>TC-DASH-003</v>
       </c>
       <c r="B24" t="str">
-        <v>TC-LOGIN-008 | Both fields empty blocked</v>
+        <v>TC-DASH-003 | OVERVIEW and ANALYTICS buttons visible</v>
       </c>
       <c r="C24" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D24" t="str">
-        <v>Boundary</v>
+        <v>UI</v>
       </c>
       <c r="E24" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="F24" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online</v>
@@ -1593,19 +1593,19 @@
     </row>
     <row r="25" xml:space="preserve">
       <c r="A25" t="str">
-        <v>TC-LOGIN-009</v>
+        <v>TC-DASH-004</v>
       </c>
       <c r="B25" t="str">
-        <v>TC-LOGIN-009 | SQL injection rejected</v>
+        <v>TC-DASH-004 | ANALYTICS tab shows analytics content</v>
       </c>
       <c r="C25" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D25" t="str">
-        <v>Security</v>
+        <v>Positive</v>
       </c>
       <c r="E25" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="F25" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online</v>
@@ -1622,10 +1622,10 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J25" t="str">
-        <v>_x001b_[31mTest timeout of 30000ms exceeded._x001b_[39m</v>
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
       </c>
       <c r="K25" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="L25" t="str">
         <v>Automation (Playwright)</v>
@@ -1634,7 +1634,7 @@
         <v>25 Jun 2026</v>
       </c>
       <c r="N25" t="str">
-        <v/>
+        <v>BUG-DASHBOARD-024</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -1642,19 +1642,19 @@
     </row>
     <row r="26" xml:space="preserve">
       <c r="A26" t="str">
-        <v>TC-LOGIN-010</v>
+        <v>TC-DASH-005</v>
       </c>
       <c r="B26" t="str">
-        <v>TC-LOGIN-010 | XSS payload rejected</v>
+        <v>TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
       </c>
       <c r="C26" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D26" t="str">
-        <v>Security</v>
+        <v>Positive</v>
       </c>
       <c r="E26" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="F26" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online</v>
@@ -1671,10 +1671,10 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J26" t="str">
-        <v>Test passed successfully</v>
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
       </c>
       <c r="K26" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="L26" t="str">
         <v>Automation (Playwright)</v>
@@ -1683,7 +1683,7 @@
         <v>25 Jun 2026</v>
       </c>
       <c r="N26" t="str">
-        <v/>
+        <v>BUG-DASHBOARD-025</v>
       </c>
       <c r="O26" t="str">
         <v/>
@@ -1691,19 +1691,19 @@
     </row>
     <row r="27" xml:space="preserve">
       <c r="A27" t="str">
-        <v>TC-LOGIN-011</v>
+        <v>TC-DASH-006</v>
       </c>
       <c r="B27" t="str">
-        <v>TC-LOGIN-011 | Max length username (256 chars) handled</v>
+        <v>TC-DASH-006 | Date range filter applies correctly</v>
       </c>
       <c r="C27" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D27" t="str">
-        <v>Boundary</v>
+        <v>Positive</v>
       </c>
       <c r="E27" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="F27" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online</v>
@@ -1740,63 +1740,1043 @@
     </row>
     <row r="28" xml:space="preserve">
       <c r="A28" t="str">
+        <v>TC-DASH-007</v>
+      </c>
+      <c r="B28" t="str">
+        <v>TC-DASH-007 | Reset button clears date filter</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G28" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('button:has-text("Reset")').first() Expected: visible Received: hidden Timeout:  5000ms  Ca</v>
+      </c>
+      <c r="K28" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M28" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N28" t="str">
+        <v>BUG-DASHBOARD-027</v>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>TC-DASH-008</v>
+      </c>
+      <c r="B29" t="str">
+        <v>TC-DASH-008 | Invalid date range To &lt; From handled gracefully</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E29" t="str">
+        <v>High</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G29" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K29" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M29" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>TC-DASH-009</v>
+      </c>
+      <c r="B30" t="str">
+        <v>TC-DASH-009 | Active Tickets table with correct columns</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G30" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K30" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M30" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
+        <v>TC-DASH-010</v>
+      </c>
+      <c r="B31" t="str">
+        <v>TC-DASH-010 | View All link navigates to ticket list</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G31" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K31" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M31" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
+        <v>TC-DASH-011</v>
+      </c>
+      <c r="B32" t="str">
+        <v>TC-DASH-011 | All sidebar navigation links present</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G32" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout:  5000ms  Cal</v>
+      </c>
+      <c r="K32" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M32" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N32" t="str">
+        <v>BUG-DASHBOARD-031</v>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>TC-DASH-012</v>
+      </c>
+      <c r="B33" t="str">
+        <v>TC-DASH-012 | Action Queue badge shows ticket count</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G33" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K33" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M33" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>TC-DASH-013</v>
+      </c>
+      <c r="B34" t="str">
+        <v>TC-DASH-013 | Search box accepts input</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G34" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K34" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M34" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>TC-DASH-014</v>
+      </c>
+      <c r="B35" t="str">
+        <v>TC-DASH-014 | User profile dropdown shows username and links</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G35" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K35" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M35" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>TC-DASH-015</v>
+      </c>
+      <c r="B36" t="str">
+        <v>TC-DASH-015 | Dashboard inaccessible without login</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G36" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K36" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M36" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>TC-LOGIN-001</v>
+      </c>
+      <c r="B37" t="str">
+        <v>TC-LOGIN-001 | Login page loads with all UI elements</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D37" t="str">
+        <v>UI</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G37" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K37" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M37" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>TC-LOGIN-002</v>
+      </c>
+      <c r="B38" t="str">
+        <v>TC-LOGIN-002 | Valid credentials redirect to dashboard</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G38" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M38" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
+        <v>TC-LOGIN-003</v>
+      </c>
+      <c r="B39" t="str">
+        <v>TC-LOGIN-003 | Login with Remember Me checked</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G39" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M39" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
+        <v>TC-LOGIN-004</v>
+      </c>
+      <c r="B40" t="str">
+        <v>TC-LOGIN-004 | Invalid username shows error</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E40" t="str">
+        <v>High</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G40" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K40" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M40" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
+        <v>TC-LOGIN-005</v>
+      </c>
+      <c r="B41" t="str">
+        <v>TC-LOGIN-005 | Invalid password shows error</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E41" t="str">
+        <v>High</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G41" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M41" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
+        <v>TC-LOGIN-006</v>
+      </c>
+      <c r="B42" t="str">
+        <v>TC-LOGIN-006 | Empty username blocked</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E42" t="str">
+        <v>High</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G42" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M42" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>TC-LOGIN-007</v>
+      </c>
+      <c r="B43" t="str">
+        <v>TC-LOGIN-007 | Empty password blocked</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E43" t="str">
+        <v>High</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G43" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K43" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M43" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
+        <v>TC-LOGIN-008</v>
+      </c>
+      <c r="B44" t="str">
+        <v>TC-LOGIN-008 | Both fields empty blocked</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E44" t="str">
+        <v>High</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G44" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K44" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M44" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
+        <v>TC-LOGIN-009</v>
+      </c>
+      <c r="B45" t="str">
+        <v>TC-LOGIN-009 | SQL injection rejected</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E45" t="str">
+        <v>High</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G45" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I45" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J45" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K45" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M45" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
+        <v>TC-LOGIN-010</v>
+      </c>
+      <c r="B46" t="str">
+        <v>TC-LOGIN-010 | XSS payload rejected</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E46" t="str">
+        <v>High</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G46" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I46" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J46" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K46" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M46" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str">
+        <v>TC-LOGIN-011</v>
+      </c>
+      <c r="B47" t="str">
+        <v>TC-LOGIN-011 | Max length username (256 chars) handled</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G47" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J47" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K47" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M47" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
         <v>TC-LOGIN-012</v>
       </c>
-      <c r="B28" t="str">
+      <c r="B48" t="str">
         <v>TC-LOGIN-012 | Password field masks input</v>
       </c>
-      <c r="C28" t="str">
-        <v>Dashboard</v>
-      </c>
-      <c r="D28" t="str">
+      <c r="C48" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D48" t="str">
         <v>UI</v>
       </c>
-      <c r="E28" t="str">
-        <v>Low</v>
-      </c>
-      <c r="F28" t="str">
-        <v>Application accessible at http://customerportal.dev-ts.online</v>
-      </c>
-      <c r="G28" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to page
-2. Perform action
-3. Verify result</v>
-      </c>
-      <c r="H28" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
-      </c>
-      <c r="I28" t="str">
-        <v>Test should pass per acceptance criteria</v>
-      </c>
-      <c r="J28" t="str">
-        <v>Test passed successfully</v>
-      </c>
-      <c r="K28" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="L28" t="str">
-        <v>Automation (Playwright)</v>
-      </c>
-      <c r="M28" t="str">
-        <v>25 Jun 2026</v>
-      </c>
-      <c r="N28" t="str">
-        <v/>
-      </c>
-      <c r="O28" t="str">
+      <c r="E48" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G48" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Username: sajith_xyz | Password: User@123</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K48" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Automation (Playwright)</v>
+      </c>
+      <c r="M48" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O48"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P11"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1871,13 +2851,13 @@
         <v>BUG-DASHBOARD-001</v>
       </c>
       <c r="B2" t="str">
-        <v>[FAIL] TC-DASH-002 | All 4 stat cards visible with values</v>
+        <v>[FAIL] TC-TICKET-005 | All Ticket Type chips are visible</v>
       </c>
       <c r="C2" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D2" t="str">
-        <v>TC-DASH-002</v>
+        <v>TC-TICKET-005</v>
       </c>
       <c r="E2" t="str">
         <v>Low</v>
@@ -1897,7 +2877,7 @@
         <v>Test should pass</v>
       </c>
       <c r="J2" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+        <v xml:space="preserve">Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('text=SCR').first() Expected: visible Received: hidden Timeout:  5000ms  Call log: _x001b_[2m  - </v>
       </c>
       <c r="K2" t="str">
         <v>New</v>
@@ -1912,7 +2892,7 @@
         <v>Not Run</v>
       </c>
       <c r="O2" t="str">
-        <v>reports/screenshots/TC-DASH-002-failure.png</v>
+        <v>reports/screenshots/TC-TICKET-005-failure.png</v>
       </c>
       <c r="P2" t="str">
         <v/>
@@ -1923,13 +2903,13 @@
         <v>BUG-DASHBOARD-002</v>
       </c>
       <c r="B3" t="str">
-        <v>[FAIL] TC-DASH-004 | ANALYTICS tab shows analytics content</v>
+        <v>[FAIL] TC-TICKET-006 | Description character counter updates on input</v>
       </c>
       <c r="C3" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D3" t="str">
-        <v>TC-DASH-004</v>
+        <v>TC-TICKET-006</v>
       </c>
       <c r="E3" t="str">
         <v>Low</v>
@@ -1949,7 +2929,7 @@
         <v>Test should pass</v>
       </c>
       <c r="J3" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mnot_x001b_[2m._x001b_[22mtoBe_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m) // Object.is equality_x001b_[22m  Expected: not _x001b_[32m"0 / 2000"_x001b_[39m</v>
       </c>
       <c r="K3" t="str">
         <v>New</v>
@@ -1964,7 +2944,7 @@
         <v>Not Run</v>
       </c>
       <c r="O3" t="str">
-        <v>reports/screenshots/TC-DASH-004-failure.png</v>
+        <v>reports/screenshots/TC-TICKET-006-failure.png</v>
       </c>
       <c r="P3" t="str">
         <v/>
@@ -1975,13 +2955,13 @@
         <v>BUG-DASHBOARD-003</v>
       </c>
       <c r="B4" t="str">
-        <v>[FAIL] TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
+        <v>[FAIL] TC-TICKET-007 | Reset button clears all filled fields</v>
       </c>
       <c r="C4" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D4" t="str">
-        <v>TC-DASH-005</v>
+        <v>TC-TICKET-007</v>
       </c>
       <c r="E4" t="str">
         <v>Low</v>
@@ -2001,7 +2981,7 @@
         <v>Test should pass</v>
       </c>
       <c r="J4" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBe_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m) // Object.is equality_x001b_[22m  Expected: _x001b_[32m""_x001b_[39m Received: _x001b_[31m"Some description text here"_x001b_[39m</v>
       </c>
       <c r="K4" t="str">
         <v>New</v>
@@ -2016,7 +2996,7 @@
         <v>Not Run</v>
       </c>
       <c r="O4" t="str">
-        <v>reports/screenshots/TC-DASH-005-failure.png</v>
+        <v>reports/screenshots/TC-TICKET-007-failure.png</v>
       </c>
       <c r="P4" t="str">
         <v/>
@@ -2027,13 +3007,13 @@
         <v>BUG-DASHBOARD-004</v>
       </c>
       <c r="B5" t="str">
-        <v>[FAIL] TC-DASH-007 | Reset button clears date filter</v>
+        <v>[FAIL] TC-TICKET-014 | Description with exactly 14 chars fails validation</v>
       </c>
       <c r="C5" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D5" t="str">
-        <v>TC-DASH-007</v>
+        <v>TC-TICKET-014</v>
       </c>
       <c r="E5" t="str">
         <v>Low</v>
@@ -2053,7 +3033,7 @@
         <v>Test should pass</v>
       </c>
       <c r="J5" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('button:has-text("Reset")').first() Expected: visible Received: hidden Timeout:  5000ms  Ca</v>
+        <v xml:space="preserve">Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoMatch_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m)_x001b_[22m  Expected pattern: _x001b_[32m/Description/i_x001b_[39m Received string:  _x001b_[31m"Are you sure you want to log this </v>
       </c>
       <c r="K5" t="str">
         <v>New</v>
@@ -2068,7 +3048,7 @@
         <v>Not Run</v>
       </c>
       <c r="O5" t="str">
-        <v>reports/screenshots/TC-DASH-007-failure.png</v>
+        <v>reports/screenshots/TC-TICKET-014-failure.png</v>
       </c>
       <c r="P5" t="str">
         <v/>
@@ -2079,16 +3059,16 @@
         <v>BUG-DASHBOARD-005</v>
       </c>
       <c r="B6" t="str">
-        <v>[FAIL] TC-DASH-011 | All sidebar navigation links present</v>
+        <v>[FAIL] TC-TICKET-016 | Description at 2000 chars (max) is accepted</v>
       </c>
       <c r="C6" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D6" t="str">
-        <v>TC-DASH-011</v>
+        <v>TC-TICKET-016</v>
       </c>
       <c r="E6" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="F6" t="str">
         <v>P3</v>
@@ -2105,7 +3085,7 @@
         <v>Test should pass</v>
       </c>
       <c r="J6" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout:  5000ms  Cal</v>
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBe_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m) // Object.is equality_x001b_[22m  Expected: _x001b_[32m2000_x001b_[39m Received: _x001b_[31m0_x001b_[39m</v>
       </c>
       <c r="K6" t="str">
         <v>New</v>
@@ -2120,15 +3100,275 @@
         <v>Not Run</v>
       </c>
       <c r="O6" t="str">
+        <v>reports/screenshots/TC-TICKET-016-failure.png</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>BUG-DASHBOARD-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>[FAIL] TC-DASH-002 | All 4 stat cards visible with values</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D7" t="str">
+        <v>TC-DASH-002</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F7" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G7" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Ubuntu</v>
+      </c>
+      <c r="H7" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate
+2. Execute test steps
+3. Observe failure</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Test should pass</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+      <c r="K7" t="str">
+        <v>New</v>
+      </c>
+      <c r="L7" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="O7" t="str">
+        <v>reports/screenshots/TC-DASH-002-failure.png</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>BUG-DASHBOARD-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>[FAIL] TC-DASH-004 | ANALYTICS tab shows analytics content</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D8" t="str">
+        <v>TC-DASH-004</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F8" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G8" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Ubuntu</v>
+      </c>
+      <c r="H8" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate
+2. Execute test steps
+3. Observe failure</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Test should pass</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+      <c r="K8" t="str">
+        <v>New</v>
+      </c>
+      <c r="L8" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="O8" t="str">
+        <v>reports/screenshots/TC-DASH-004-failure.png</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>BUG-DASHBOARD-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>[FAIL] TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D9" t="str">
+        <v>TC-DASH-005</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F9" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G9" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Ubuntu</v>
+      </c>
+      <c r="H9" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate
+2. Execute test steps
+3. Observe failure</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Test should pass</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+      <c r="K9" t="str">
+        <v>New</v>
+      </c>
+      <c r="L9" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="O9" t="str">
+        <v>reports/screenshots/TC-DASH-005-failure.png</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>BUG-DASHBOARD-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>[FAIL] TC-DASH-007 | Reset button clears date filter</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D10" t="str">
+        <v>TC-DASH-007</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F10" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G10" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Ubuntu</v>
+      </c>
+      <c r="H10" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate
+2. Execute test steps
+3. Observe failure</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Test should pass</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('button:has-text("Reset")').first() Expected: visible Received: hidden Timeout:  5000ms  Ca</v>
+      </c>
+      <c r="K10" t="str">
+        <v>New</v>
+      </c>
+      <c r="L10" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="O10" t="str">
+        <v>reports/screenshots/TC-DASH-007-failure.png</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
+        <v>BUG-DASHBOARD-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>[FAIL] TC-DASH-011 | All sidebar navigation links present</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D11" t="str">
+        <v>TC-DASH-011</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F11" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G11" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Ubuntu</v>
+      </c>
+      <c r="H11" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate
+2. Execute test steps
+3. Observe failure</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Test should pass</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout:  5000ms  Cal</v>
+      </c>
+      <c r="K11" t="str">
+        <v>New</v>
+      </c>
+      <c r="L11" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="O11" t="str">
         <v>reports/screenshots/TC-DASH-011-failure.png</v>
       </c>
-      <c r="P6" t="str">
+      <c r="P11" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Test Execution Report/Feature Reports/Dashboard.xlsx
+++ b/Test Execution Report/Feature Reports/Dashboard.xlsx
@@ -691,10 +691,10 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J6" t="str">
-        <v xml:space="preserve">Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('text=SCR').first() Expected: visible Received: hidden Timeout:  5000ms  Call log: _x001b_[2m  - </v>
+        <v>Test passed successfully</v>
       </c>
       <c r="K6" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L6" t="str">
         <v>Automation (Playwright)</v>
@@ -703,7 +703,7 @@
         <v>25 Jun 2026</v>
       </c>
       <c r="N6" t="str">
-        <v>BUG-DASHBOARD-005</v>
+        <v/>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -740,10 +740,10 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J7" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mnot_x001b_[2m._x001b_[22mtoBe_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m) // Object.is equality_x001b_[22m  Expected: not _x001b_[32m"0 / 2000"_x001b_[39m</v>
+        <v>Test passed successfully</v>
       </c>
       <c r="K7" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L7" t="str">
         <v>Automation (Playwright)</v>
@@ -752,7 +752,7 @@
         <v>25 Jun 2026</v>
       </c>
       <c r="N7" t="str">
-        <v>BUG-DASHBOARD-006</v>
+        <v/>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -789,10 +789,10 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J8" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBe_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m) // Object.is equality_x001b_[22m  Expected: _x001b_[32m""_x001b_[39m Received: _x001b_[31m"Some description text here"_x001b_[39m</v>
+        <v>Test passed successfully</v>
       </c>
       <c r="K8" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L8" t="str">
         <v>Automation (Playwright)</v>
@@ -801,7 +801,7 @@
         <v>25 Jun 2026</v>
       </c>
       <c r="N8" t="str">
-        <v>BUG-DASHBOARD-007</v>
+        <v/>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -1132,10 +1132,10 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J15" t="str">
-        <v xml:space="preserve">Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoMatch_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m)_x001b_[22m  Expected pattern: _x001b_[32m/Description/i_x001b_[39m Received string:  _x001b_[31m"Are you sure you want to log this </v>
+        <v>Test passed successfully</v>
       </c>
       <c r="K15" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L15" t="str">
         <v>Automation (Playwright)</v>
@@ -1144,7 +1144,7 @@
         <v>25 Jun 2026</v>
       </c>
       <c r="N15" t="str">
-        <v>BUG-DASHBOARD-014</v>
+        <v/>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -1230,10 +1230,10 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J17" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBe_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m) // Object.is equality_x001b_[22m  Expected: _x001b_[32m2000_x001b_[39m Received: _x001b_[31m0_x001b_[39m</v>
+        <v>Test passed successfully</v>
       </c>
       <c r="K17" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L17" t="str">
         <v>Automation (Playwright)</v>
@@ -1242,7 +1242,7 @@
         <v>25 Jun 2026</v>
       </c>
       <c r="N17" t="str">
-        <v>BUG-DASHBOARD-016</v>
+        <v/>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -2776,7 +2776,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P6"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -2851,13 +2851,13 @@
         <v>BUG-DASHBOARD-001</v>
       </c>
       <c r="B2" t="str">
-        <v>[FAIL] TC-TICKET-005 | All Ticket Type chips are visible</v>
+        <v>[FAIL] TC-DASH-002 | All 4 stat cards visible with values</v>
       </c>
       <c r="C2" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D2" t="str">
-        <v>TC-TICKET-005</v>
+        <v>TC-DASH-002</v>
       </c>
       <c r="E2" t="str">
         <v>Low</v>
@@ -2877,7 +2877,7 @@
         <v>Test should pass</v>
       </c>
       <c r="J2" t="str">
-        <v xml:space="preserve">Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('text=SCR').first() Expected: visible Received: hidden Timeout:  5000ms  Call log: _x001b_[2m  - </v>
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
       </c>
       <c r="K2" t="str">
         <v>New</v>
@@ -2892,7 +2892,7 @@
         <v>Not Run</v>
       </c>
       <c r="O2" t="str">
-        <v>reports/screenshots/TC-TICKET-005-failure.png</v>
+        <v>reports/screenshots/TC-DASH-002-failure.png</v>
       </c>
       <c r="P2" t="str">
         <v/>
@@ -2903,13 +2903,13 @@
         <v>BUG-DASHBOARD-002</v>
       </c>
       <c r="B3" t="str">
-        <v>[FAIL] TC-TICKET-006 | Description character counter updates on input</v>
+        <v>[FAIL] TC-DASH-004 | ANALYTICS tab shows analytics content</v>
       </c>
       <c r="C3" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D3" t="str">
-        <v>TC-TICKET-006</v>
+        <v>TC-DASH-004</v>
       </c>
       <c r="E3" t="str">
         <v>Low</v>
@@ -2929,7 +2929,7 @@
         <v>Test should pass</v>
       </c>
       <c r="J3" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mnot_x001b_[2m._x001b_[22mtoBe_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m) // Object.is equality_x001b_[22m  Expected: not _x001b_[32m"0 / 2000"_x001b_[39m</v>
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
       </c>
       <c r="K3" t="str">
         <v>New</v>
@@ -2944,7 +2944,7 @@
         <v>Not Run</v>
       </c>
       <c r="O3" t="str">
-        <v>reports/screenshots/TC-TICKET-006-failure.png</v>
+        <v>reports/screenshots/TC-DASH-004-failure.png</v>
       </c>
       <c r="P3" t="str">
         <v/>
@@ -2955,13 +2955,13 @@
         <v>BUG-DASHBOARD-003</v>
       </c>
       <c r="B4" t="str">
-        <v>[FAIL] TC-TICKET-007 | Reset button clears all filled fields</v>
+        <v>[FAIL] TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
       </c>
       <c r="C4" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D4" t="str">
-        <v>TC-TICKET-007</v>
+        <v>TC-DASH-005</v>
       </c>
       <c r="E4" t="str">
         <v>Low</v>
@@ -2981,7 +2981,7 @@
         <v>Test should pass</v>
       </c>
       <c r="J4" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBe_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m) // Object.is equality_x001b_[22m  Expected: _x001b_[32m""_x001b_[39m Received: _x001b_[31m"Some description text here"_x001b_[39m</v>
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
       </c>
       <c r="K4" t="str">
         <v>New</v>
@@ -2996,7 +2996,7 @@
         <v>Not Run</v>
       </c>
       <c r="O4" t="str">
-        <v>reports/screenshots/TC-TICKET-007-failure.png</v>
+        <v>reports/screenshots/TC-DASH-005-failure.png</v>
       </c>
       <c r="P4" t="str">
         <v/>
@@ -3007,13 +3007,13 @@
         <v>BUG-DASHBOARD-004</v>
       </c>
       <c r="B5" t="str">
-        <v>[FAIL] TC-TICKET-014 | Description with exactly 14 chars fails validation</v>
+        <v>[FAIL] TC-DASH-007 | Reset button clears date filter</v>
       </c>
       <c r="C5" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D5" t="str">
-        <v>TC-TICKET-014</v>
+        <v>TC-DASH-007</v>
       </c>
       <c r="E5" t="str">
         <v>Low</v>
@@ -3033,7 +3033,7 @@
         <v>Test should pass</v>
       </c>
       <c r="J5" t="str">
-        <v xml:space="preserve">Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoMatch_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m)_x001b_[22m  Expected pattern: _x001b_[32m/Description/i_x001b_[39m Received string:  _x001b_[31m"Are you sure you want to log this </v>
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('button:has-text("Reset")').first() Expected: visible Received: hidden Timeout:  5000ms  Ca</v>
       </c>
       <c r="K5" t="str">
         <v>New</v>
@@ -3048,7 +3048,7 @@
         <v>Not Run</v>
       </c>
       <c r="O5" t="str">
-        <v>reports/screenshots/TC-TICKET-014-failure.png</v>
+        <v>reports/screenshots/TC-DASH-007-failure.png</v>
       </c>
       <c r="P5" t="str">
         <v/>
@@ -3059,16 +3059,16 @@
         <v>BUG-DASHBOARD-005</v>
       </c>
       <c r="B6" t="str">
-        <v>[FAIL] TC-TICKET-016 | Description at 2000 chars (max) is accepted</v>
+        <v>[FAIL] TC-DASH-011 | All sidebar navigation links present</v>
       </c>
       <c r="C6" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D6" t="str">
-        <v>TC-TICKET-016</v>
+        <v>TC-DASH-011</v>
       </c>
       <c r="E6" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="F6" t="str">
         <v>P3</v>
@@ -3085,7 +3085,7 @@
         <v>Test should pass</v>
       </c>
       <c r="J6" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBe_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m) // Object.is equality_x001b_[22m  Expected: _x001b_[32m2000_x001b_[39m Received: _x001b_[31m0_x001b_[39m</v>
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout:  5000ms  Cal</v>
       </c>
       <c r="K6" t="str">
         <v>New</v>
@@ -3100,275 +3100,15 @@
         <v>Not Run</v>
       </c>
       <c r="O6" t="str">
-        <v>reports/screenshots/TC-TICKET-016-failure.png</v>
+        <v>reports/screenshots/TC-DASH-011-failure.png</v>
       </c>
       <c r="P6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7" t="str">
-        <v>BUG-DASHBOARD-006</v>
-      </c>
-      <c r="B7" t="str">
-        <v>[FAIL] TC-DASH-002 | All 4 stat cards visible with values</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Dashboard</v>
-      </c>
-      <c r="D7" t="str">
-        <v>TC-DASH-002</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Low</v>
-      </c>
-      <c r="F7" t="str">
-        <v>P3</v>
-      </c>
-      <c r="G7" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Ubuntu</v>
-      </c>
-      <c r="H7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate
-2. Execute test steps
-3. Observe failure</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Test should pass</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
-      </c>
-      <c r="K7" t="str">
-        <v>New</v>
-      </c>
-      <c r="L7" t="str">
-        <v>25 Jun 2026</v>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O7" t="str">
-        <v>reports/screenshots/TC-DASH-002-failure.png</v>
-      </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8" xml:space="preserve">
-      <c r="A8" t="str">
-        <v>BUG-DASHBOARD-007</v>
-      </c>
-      <c r="B8" t="str">
-        <v>[FAIL] TC-DASH-004 | ANALYTICS tab shows analytics content</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Dashboard</v>
-      </c>
-      <c r="D8" t="str">
-        <v>TC-DASH-004</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Low</v>
-      </c>
-      <c r="F8" t="str">
-        <v>P3</v>
-      </c>
-      <c r="G8" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Ubuntu</v>
-      </c>
-      <c r="H8" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate
-2. Execute test steps
-3. Observe failure</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Test should pass</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
-      </c>
-      <c r="K8" t="str">
-        <v>New</v>
-      </c>
-      <c r="L8" t="str">
-        <v>25 Jun 2026</v>
-      </c>
-      <c r="M8" t="str">
-        <v/>
-      </c>
-      <c r="N8" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O8" t="str">
-        <v>reports/screenshots/TC-DASH-004-failure.png</v>
-      </c>
-      <c r="P8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9" t="str">
-        <v>BUG-DASHBOARD-008</v>
-      </c>
-      <c r="B9" t="str">
-        <v>[FAIL] TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Dashboard</v>
-      </c>
-      <c r="D9" t="str">
-        <v>TC-DASH-005</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Low</v>
-      </c>
-      <c r="F9" t="str">
-        <v>P3</v>
-      </c>
-      <c r="G9" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Ubuntu</v>
-      </c>
-      <c r="H9" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate
-2. Execute test steps
-3. Observe failure</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Test should pass</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
-      </c>
-      <c r="K9" t="str">
-        <v>New</v>
-      </c>
-      <c r="L9" t="str">
-        <v>25 Jun 2026</v>
-      </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
-      <c r="N9" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O9" t="str">
-        <v>reports/screenshots/TC-DASH-005-failure.png</v>
-      </c>
-      <c r="P9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str">
-        <v>BUG-DASHBOARD-009</v>
-      </c>
-      <c r="B10" t="str">
-        <v>[FAIL] TC-DASH-007 | Reset button clears date filter</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Dashboard</v>
-      </c>
-      <c r="D10" t="str">
-        <v>TC-DASH-007</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Low</v>
-      </c>
-      <c r="F10" t="str">
-        <v>P3</v>
-      </c>
-      <c r="G10" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Ubuntu</v>
-      </c>
-      <c r="H10" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate
-2. Execute test steps
-3. Observe failure</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Test should pass</v>
-      </c>
-      <c r="J10" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('button:has-text("Reset")').first() Expected: visible Received: hidden Timeout:  5000ms  Ca</v>
-      </c>
-      <c r="K10" t="str">
-        <v>New</v>
-      </c>
-      <c r="L10" t="str">
-        <v>25 Jun 2026</v>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-      <c r="N10" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O10" t="str">
-        <v>reports/screenshots/TC-DASH-007-failure.png</v>
-      </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11" t="str">
-        <v>BUG-DASHBOARD-010</v>
-      </c>
-      <c r="B11" t="str">
-        <v>[FAIL] TC-DASH-011 | All sidebar navigation links present</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Dashboard</v>
-      </c>
-      <c r="D11" t="str">
-        <v>TC-DASH-011</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Low</v>
-      </c>
-      <c r="F11" t="str">
-        <v>P3</v>
-      </c>
-      <c r="G11" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Ubuntu</v>
-      </c>
-      <c r="H11" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate
-2. Execute test steps
-3. Observe failure</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Test should pass</v>
-      </c>
-      <c r="J11" t="str">
-        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout:  5000ms  Cal</v>
-      </c>
-      <c r="K11" t="str">
-        <v>New</v>
-      </c>
-      <c r="L11" t="str">
-        <v>25 Jun 2026</v>
-      </c>
-      <c r="M11" t="str">
-        <v/>
-      </c>
-      <c r="N11" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O11" t="str">
-        <v>reports/screenshots/TC-DASH-011-failure.png</v>
-      </c>
-      <c r="P11" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Test Execution Report/Feature Reports/Dashboard.xlsx
+++ b/Test Execution Report/Feature Reports/Dashboard.xlsx
@@ -2602,10 +2602,10 @@
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J45" t="str">
-        <v>_x001b_[31mTest timeout of 30000ms exceeded._x001b_[39m</v>
+        <v>Test passed successfully</v>
       </c>
       <c r="K45" t="str">
-        <v>NOT RUN</v>
+        <v>PASS</v>
       </c>
       <c r="L45" t="str">
         <v>Automation (Playwright)</v>

--- a/Test Execution Report/Feature Reports/Dashboard.xlsx
+++ b/Test Execution Report/Feature Reports/Dashboard.xlsx
@@ -403,29 +403,29 @@
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="45.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="30.83203125" customWidth="1"/>
-    <col min="7" max="7" width="40.83203125" customWidth="1"/>
+    <col min="7" max="7" width="42.83203125" customWidth="1"/>
     <col min="8" max="8" width="30.83203125" customWidth="1"/>
-    <col min="9" max="9" width="35.83203125" customWidth="1"/>
+    <col min="9" max="9" width="38.83203125" customWidth="1"/>
     <col min="10" max="10" width="45.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
-    <col min="12" max="12" width="22.83203125" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" customWidth="1"/>
     <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="14.83203125" customWidth="1"/>
-    <col min="15" max="15" width="25.83203125" customWidth="1"/>
+    <col min="14" max="14" width="42.83203125" customWidth="1"/>
+    <col min="15" max="15" width="28.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Test Case ID</v>
+        <v>TC ID</v>
       </c>
       <c r="B1" t="str">
         <v>Test Case Name</v>
       </c>
       <c r="C1" t="str">
-        <v>Module / Feature</v>
+        <v>Module</v>
       </c>
       <c r="D1" t="str">
         <v>Test Type</v>
@@ -458,7 +458,7 @@
         <v>Execution Date</v>
       </c>
       <c r="N1" t="str">
-        <v>Defect ID</v>
+        <v>Environment</v>
       </c>
       <c r="O1" t="str">
         <v>Remarks</v>
@@ -475,7 +475,7 @@
         <v>Dashboard</v>
       </c>
       <c r="D2" t="str">
-        <v>UI</v>
+        <v>Positive</v>
       </c>
       <c r="E2" t="str">
         <v>Critical</v>
@@ -489,7 +489,7 @@
 3. Verify result</v>
       </c>
       <c r="H2" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I2" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -501,13 +501,13 @@
         <v>PASS</v>
       </c>
       <c r="L2" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M2" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O2" t="str">
         <v/>
@@ -524,7 +524,7 @@
         <v>Dashboard</v>
       </c>
       <c r="D3" t="str">
-        <v>UI</v>
+        <v>Positive</v>
       </c>
       <c r="E3" t="str">
         <v>Low</v>
@@ -538,7 +538,7 @@
 3. Verify result</v>
       </c>
       <c r="H3" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I3" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -550,13 +550,13 @@
         <v>PASS</v>
       </c>
       <c r="L3" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M3" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O3" t="str">
         <v/>
@@ -587,7 +587,7 @@
 3. Verify result</v>
       </c>
       <c r="H4" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I4" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -599,13 +599,13 @@
         <v>PASS</v>
       </c>
       <c r="L4" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M4" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -636,7 +636,7 @@
 3. Verify result</v>
       </c>
       <c r="H5" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I5" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -648,13 +648,13 @@
         <v>PASS</v>
       </c>
       <c r="L5" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M5" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N5" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -671,7 +671,7 @@
         <v>Dashboard</v>
       </c>
       <c r="D6" t="str">
-        <v>UI</v>
+        <v>Positive</v>
       </c>
       <c r="E6" t="str">
         <v>Low</v>
@@ -685,7 +685,7 @@
 3. Verify result</v>
       </c>
       <c r="H6" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I6" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -697,13 +697,13 @@
         <v>PASS</v>
       </c>
       <c r="L6" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M6" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -734,7 +734,7 @@
 3. Verify result</v>
       </c>
       <c r="H7" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I7" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -746,13 +746,13 @@
         <v>PASS</v>
       </c>
       <c r="L7" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M7" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -783,7 +783,7 @@
 3. Verify result</v>
       </c>
       <c r="H8" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I8" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -795,13 +795,13 @@
         <v>PASS</v>
       </c>
       <c r="L8" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M8" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N8" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -832,7 +832,7 @@
 3. Verify result</v>
       </c>
       <c r="H9" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I9" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -844,13 +844,13 @@
         <v>PASS</v>
       </c>
       <c r="L9" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M9" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N9" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -881,7 +881,7 @@
 3. Verify result</v>
       </c>
       <c r="H10" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I10" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -893,13 +893,13 @@
         <v>PASS</v>
       </c>
       <c r="L10" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M10" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N10" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -930,7 +930,7 @@
 3. Verify result</v>
       </c>
       <c r="H11" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I11" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -942,13 +942,13 @@
         <v>PASS</v>
       </c>
       <c r="L11" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M11" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -979,7 +979,7 @@
 3. Verify result</v>
       </c>
       <c r="H12" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I12" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -991,13 +991,13 @@
         <v>PASS</v>
       </c>
       <c r="L12" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M12" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N12" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -1028,7 +1028,7 @@
 3. Verify result</v>
       </c>
       <c r="H13" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I13" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1040,13 +1040,13 @@
         <v>PASS</v>
       </c>
       <c r="L13" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M13" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N13" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -1077,7 +1077,7 @@
 3. Verify result</v>
       </c>
       <c r="H14" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I14" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1089,13 +1089,13 @@
         <v>PASS</v>
       </c>
       <c r="L14" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M14" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -1126,7 +1126,7 @@
 3. Verify result</v>
       </c>
       <c r="H15" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I15" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1138,13 +1138,13 @@
         <v>PASS</v>
       </c>
       <c r="L15" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M15" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N15" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -1175,7 +1175,7 @@
 3. Verify result</v>
       </c>
       <c r="H16" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I16" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1187,13 +1187,13 @@
         <v>PASS</v>
       </c>
       <c r="L16" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M16" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N16" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -1224,7 +1224,7 @@
 3. Verify result</v>
       </c>
       <c r="H17" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I17" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1236,13 +1236,13 @@
         <v>PASS</v>
       </c>
       <c r="L17" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M17" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -1273,7 +1273,7 @@
 3. Verify result</v>
       </c>
       <c r="H18" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I18" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1285,13 +1285,13 @@
         <v>PASS</v>
       </c>
       <c r="L18" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M18" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O18" t="str">
         <v/>
@@ -1322,7 +1322,7 @@
 3. Verify result</v>
       </c>
       <c r="H19" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I19" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1334,13 +1334,13 @@
         <v>PASS</v>
       </c>
       <c r="L19" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M19" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O19" t="str">
         <v/>
@@ -1371,7 +1371,7 @@
 3. Verify result</v>
       </c>
       <c r="H20" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I20" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1383,13 +1383,13 @@
         <v>PASS</v>
       </c>
       <c r="L20" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M20" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N20" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O20" t="str">
         <v/>
@@ -1406,10 +1406,10 @@
         <v>Dashboard</v>
       </c>
       <c r="D21" t="str">
-        <v>Positive</v>
+        <v>Security</v>
       </c>
       <c r="E21" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="F21" t="str">
         <v>Application accessible at http://customerportal.dev-ts.online</v>
@@ -1420,7 +1420,7 @@
 3. Verify result</v>
       </c>
       <c r="H21" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I21" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1432,13 +1432,13 @@
         <v>PASS</v>
       </c>
       <c r="L21" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M21" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N21" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O21" t="str">
         <v/>
@@ -1455,7 +1455,7 @@
         <v>Dashboard</v>
       </c>
       <c r="D22" t="str">
-        <v>UI</v>
+        <v>Positive</v>
       </c>
       <c r="E22" t="str">
         <v>Critical</v>
@@ -1469,7 +1469,7 @@
 3. Verify result</v>
       </c>
       <c r="H22" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I22" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1481,13 +1481,13 @@
         <v>PASS</v>
       </c>
       <c r="L22" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M22" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N22" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O22" t="str">
         <v/>
@@ -1504,7 +1504,7 @@
         <v>Dashboard</v>
       </c>
       <c r="D23" t="str">
-        <v>UI</v>
+        <v>Positive</v>
       </c>
       <c r="E23" t="str">
         <v>Low</v>
@@ -1518,7 +1518,7 @@
 3. Verify result</v>
       </c>
       <c r="H23" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I23" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1530,13 +1530,13 @@
         <v>FAIL</v>
       </c>
       <c r="L23" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M23" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N23" t="str">
-        <v>BUG-DASHBOARD-022</v>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -1553,7 +1553,7 @@
         <v>Dashboard</v>
       </c>
       <c r="D24" t="str">
-        <v>UI</v>
+        <v>Positive</v>
       </c>
       <c r="E24" t="str">
         <v>Low</v>
@@ -1567,7 +1567,7 @@
 3. Verify result</v>
       </c>
       <c r="H24" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I24" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1579,13 +1579,13 @@
         <v>PASS</v>
       </c>
       <c r="L24" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M24" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N24" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -1616,7 +1616,7 @@
 3. Verify result</v>
       </c>
       <c r="H25" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I25" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1628,13 +1628,13 @@
         <v>FAIL</v>
       </c>
       <c r="L25" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M25" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N25" t="str">
-        <v>BUG-DASHBOARD-024</v>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -1665,7 +1665,7 @@
 3. Verify result</v>
       </c>
       <c r="H26" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I26" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1677,13 +1677,13 @@
         <v>FAIL</v>
       </c>
       <c r="L26" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M26" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N26" t="str">
-        <v>BUG-DASHBOARD-025</v>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O26" t="str">
         <v/>
@@ -1714,7 +1714,7 @@
 3. Verify result</v>
       </c>
       <c r="H27" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I27" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1726,13 +1726,13 @@
         <v>PASS</v>
       </c>
       <c r="L27" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M27" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N27" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O27" t="str">
         <v/>
@@ -1763,7 +1763,7 @@
 3. Verify result</v>
       </c>
       <c r="H28" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I28" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1775,13 +1775,13 @@
         <v>FAIL</v>
       </c>
       <c r="L28" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M28" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N28" t="str">
-        <v>BUG-DASHBOARD-027</v>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O28" t="str">
         <v/>
@@ -1812,7 +1812,7 @@
 3. Verify result</v>
       </c>
       <c r="H29" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I29" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1824,13 +1824,13 @@
         <v>PASS</v>
       </c>
       <c r="L29" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M29" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N29" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O29" t="str">
         <v/>
@@ -1861,7 +1861,7 @@
 3. Verify result</v>
       </c>
       <c r="H30" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I30" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1873,13 +1873,13 @@
         <v>PASS</v>
       </c>
       <c r="L30" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M30" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N30" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O30" t="str">
         <v/>
@@ -1910,7 +1910,7 @@
 3. Verify result</v>
       </c>
       <c r="H31" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I31" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1922,13 +1922,13 @@
         <v>PASS</v>
       </c>
       <c r="L31" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M31" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N31" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O31" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
 3. Verify result</v>
       </c>
       <c r="H32" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I32" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -1971,13 +1971,13 @@
         <v>FAIL</v>
       </c>
       <c r="L32" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M32" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N32" t="str">
-        <v>BUG-DASHBOARD-031</v>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O32" t="str">
         <v/>
@@ -2008,7 +2008,7 @@
 3. Verify result</v>
       </c>
       <c r="H33" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I33" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -2020,13 +2020,13 @@
         <v>PASS</v>
       </c>
       <c r="L33" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M33" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N33" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O33" t="str">
         <v/>
@@ -2057,7 +2057,7 @@
 3. Verify result</v>
       </c>
       <c r="H34" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I34" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -2069,13 +2069,13 @@
         <v>PASS</v>
       </c>
       <c r="L34" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M34" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N34" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -2106,7 +2106,7 @@
 3. Verify result</v>
       </c>
       <c r="H35" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I35" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -2118,13 +2118,13 @@
         <v>PASS</v>
       </c>
       <c r="L35" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M35" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N35" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
 3. Verify result</v>
       </c>
       <c r="H36" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I36" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -2167,13 +2167,13 @@
         <v>PASS</v>
       </c>
       <c r="L36" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M36" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N36" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -2190,7 +2190,7 @@
         <v>Dashboard</v>
       </c>
       <c r="D37" t="str">
-        <v>UI</v>
+        <v>Positive</v>
       </c>
       <c r="E37" t="str">
         <v>Critical</v>
@@ -2204,7 +2204,7 @@
 3. Verify result</v>
       </c>
       <c r="H37" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I37" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -2216,13 +2216,13 @@
         <v>PASS</v>
       </c>
       <c r="L37" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M37" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N37" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O37" t="str">
         <v/>
@@ -2253,7 +2253,7 @@
 3. Verify result</v>
       </c>
       <c r="H38" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I38" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -2265,13 +2265,13 @@
         <v>PASS</v>
       </c>
       <c r="L38" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M38" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N38" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -2302,7 +2302,7 @@
 3. Verify result</v>
       </c>
       <c r="H39" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I39" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -2314,13 +2314,13 @@
         <v>PASS</v>
       </c>
       <c r="L39" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M39" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N39" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -2351,7 +2351,7 @@
 3. Verify result</v>
       </c>
       <c r="H40" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I40" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -2363,13 +2363,13 @@
         <v>PASS</v>
       </c>
       <c r="L40" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M40" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N40" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O40" t="str">
         <v/>
@@ -2400,7 +2400,7 @@
 3. Verify result</v>
       </c>
       <c r="H41" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I41" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -2412,13 +2412,13 @@
         <v>PASS</v>
       </c>
       <c r="L41" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M41" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N41" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O41" t="str">
         <v/>
@@ -2435,7 +2435,7 @@
         <v>Dashboard</v>
       </c>
       <c r="D42" t="str">
-        <v>Boundary</v>
+        <v>Negative</v>
       </c>
       <c r="E42" t="str">
         <v>High</v>
@@ -2449,7 +2449,7 @@
 3. Verify result</v>
       </c>
       <c r="H42" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I42" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -2461,13 +2461,13 @@
         <v>PASS</v>
       </c>
       <c r="L42" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M42" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N42" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O42" t="str">
         <v/>
@@ -2484,7 +2484,7 @@
         <v>Dashboard</v>
       </c>
       <c r="D43" t="str">
-        <v>Boundary</v>
+        <v>Negative</v>
       </c>
       <c r="E43" t="str">
         <v>High</v>
@@ -2498,7 +2498,7 @@
 3. Verify result</v>
       </c>
       <c r="H43" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I43" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -2510,13 +2510,13 @@
         <v>PASS</v>
       </c>
       <c r="L43" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M43" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N43" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -2533,7 +2533,7 @@
         <v>Dashboard</v>
       </c>
       <c r="D44" t="str">
-        <v>Boundary</v>
+        <v>Negative</v>
       </c>
       <c r="E44" t="str">
         <v>High</v>
@@ -2547,7 +2547,7 @@
 3. Verify result</v>
       </c>
       <c r="H44" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I44" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -2559,13 +2559,13 @@
         <v>PASS</v>
       </c>
       <c r="L44" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M44" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N44" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -2596,25 +2596,25 @@
 3. Verify result</v>
       </c>
       <c r="H45" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I45" t="str">
         <v>Test should pass per acceptance criteria</v>
       </c>
       <c r="J45" t="str">
-        <v>Test passed successfully</v>
+        <v>_x001b_[31mTest timeout of 30000ms exceeded._x001b_[39m</v>
       </c>
       <c r="K45" t="str">
-        <v>PASS</v>
+        <v>NOT RUN</v>
       </c>
       <c r="L45" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M45" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N45" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -2645,7 +2645,7 @@
 3. Verify result</v>
       </c>
       <c r="H46" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I46" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -2657,13 +2657,13 @@
         <v>PASS</v>
       </c>
       <c r="L46" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M46" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N46" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -2694,7 +2694,7 @@
 3. Verify result</v>
       </c>
       <c r="H47" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I47" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -2706,13 +2706,13 @@
         <v>PASS</v>
       </c>
       <c r="L47" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M47" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N47" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O47" t="str">
         <v/>
@@ -2729,7 +2729,7 @@
         <v>Dashboard</v>
       </c>
       <c r="D48" t="str">
-        <v>UI</v>
+        <v>Positive</v>
       </c>
       <c r="E48" t="str">
         <v>Low</v>
@@ -2743,7 +2743,7 @@
 3. Verify result</v>
       </c>
       <c r="H48" t="str">
-        <v>Username: sajith_xyz | Password: User@123</v>
+        <v>Refer to test-data/dashboardData.js</v>
       </c>
       <c r="I48" t="str">
         <v>Test should pass per acceptance criteria</v>
@@ -2755,13 +2755,13 @@
         <v>PASS</v>
       </c>
       <c r="L48" t="str">
-        <v>Automation (Playwright)</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M48" t="str">
         <v>25 Jun 2026</v>
       </c>
       <c r="N48" t="str">
-        <v/>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O48" t="str">
         <v/>
@@ -2785,14 +2785,14 @@
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="8.83203125" customWidth="1"/>
     <col min="7" max="7" width="42.83203125" customWidth="1"/>
-    <col min="8" max="8" width="40.83203125" customWidth="1"/>
+    <col min="8" max="8" width="42.83203125" customWidth="1"/>
     <col min="9" max="9" width="35.83203125" customWidth="1"/>
     <col min="10" max="10" width="45.83203125" customWidth="1"/>
     <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" customWidth="1"/>
-    <col min="14" max="14" width="16.83203125" customWidth="1"/>
-    <col min="15" max="15" width="35.83203125" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="16.83203125" customWidth="1"/>
     <col min="16" max="16" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2804,7 +2804,7 @@
         <v>Title</v>
       </c>
       <c r="C1" t="str">
-        <v>Module / Feature</v>
+        <v>Module</v>
       </c>
       <c r="D1" t="str">
         <v>Linked TC ID</v>
@@ -2831,16 +2831,16 @@
         <v>Status</v>
       </c>
       <c r="L1" t="str">
+        <v>Reported By</v>
+      </c>
+      <c r="M1" t="str">
         <v>Reported Date</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>Fixed Date</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Regression Status</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Screenshot / Evidence</v>
       </c>
       <c r="P1" t="str">
         <v>Remarks</v>
@@ -2866,15 +2866,15 @@
         <v>P3</v>
       </c>
       <c r="G2" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Ubuntu</v>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="H2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate
+        <v xml:space="preserve">1. Navigate to feature page
 2. Execute test steps
 3. Observe failure</v>
       </c>
       <c r="I2" t="str">
-        <v>Test should pass</v>
+        <v>Test should pass successfully</v>
       </c>
       <c r="J2" t="str">
         <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
@@ -2883,16 +2883,16 @@
         <v>New</v>
       </c>
       <c r="L2" t="str">
-        <v>25 Jun 2026</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
         <v>Not Run</v>
-      </c>
-      <c r="O2" t="str">
-        <v>reports/screenshots/TC-DASH-002-failure.png</v>
       </c>
       <c r="P2" t="str">
         <v/>
@@ -2918,15 +2918,15 @@
         <v>P3</v>
       </c>
       <c r="G3" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Ubuntu</v>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="H3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate
+        <v xml:space="preserve">1. Navigate to feature page
 2. Execute test steps
 3. Observe failure</v>
       </c>
       <c r="I3" t="str">
-        <v>Test should pass</v>
+        <v>Test should pass successfully</v>
       </c>
       <c r="J3" t="str">
         <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
@@ -2935,16 +2935,16 @@
         <v>New</v>
       </c>
       <c r="L3" t="str">
-        <v>25 Jun 2026</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
         <v>Not Run</v>
-      </c>
-      <c r="O3" t="str">
-        <v>reports/screenshots/TC-DASH-004-failure.png</v>
       </c>
       <c r="P3" t="str">
         <v/>
@@ -2970,15 +2970,15 @@
         <v>P3</v>
       </c>
       <c r="G4" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Ubuntu</v>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="H4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate
+        <v xml:space="preserve">1. Navigate to feature page
 2. Execute test steps
 3. Observe failure</v>
       </c>
       <c r="I4" t="str">
-        <v>Test should pass</v>
+        <v>Test should pass successfully</v>
       </c>
       <c r="J4" t="str">
         <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
@@ -2987,16 +2987,16 @@
         <v>New</v>
       </c>
       <c r="L4" t="str">
-        <v>25 Jun 2026</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
         <v>Not Run</v>
-      </c>
-      <c r="O4" t="str">
-        <v>reports/screenshots/TC-DASH-005-failure.png</v>
       </c>
       <c r="P4" t="str">
         <v/>
@@ -3022,15 +3022,15 @@
         <v>P3</v>
       </c>
       <c r="G5" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Ubuntu</v>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="H5" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate
+        <v xml:space="preserve">1. Navigate to feature page
 2. Execute test steps
 3. Observe failure</v>
       </c>
       <c r="I5" t="str">
-        <v>Test should pass</v>
+        <v>Test should pass successfully</v>
       </c>
       <c r="J5" t="str">
         <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('button:has-text("Reset")').first() Expected: visible Received: hidden Timeout:  5000ms  Ca</v>
@@ -3039,16 +3039,16 @@
         <v>New</v>
       </c>
       <c r="L5" t="str">
-        <v>25 Jun 2026</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
         <v>Not Run</v>
-      </c>
-      <c r="O5" t="str">
-        <v>reports/screenshots/TC-DASH-007-failure.png</v>
       </c>
       <c r="P5" t="str">
         <v/>
@@ -3074,15 +3074,15 @@
         <v>P3</v>
       </c>
       <c r="G6" t="str">
-        <v>http://customerportal.dev-ts.online | Chrome | Ubuntu</v>
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="H6" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate
+        <v xml:space="preserve">1. Navigate to feature page
 2. Execute test steps
 3. Observe failure</v>
       </c>
       <c r="I6" t="str">
-        <v>Test should pass</v>
+        <v>Test should pass successfully</v>
       </c>
       <c r="J6" t="str">
         <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout:  5000ms  Cal</v>
@@ -3091,16 +3091,16 @@
         <v>New</v>
       </c>
       <c r="L6" t="str">
-        <v>25 Jun 2026</v>
+        <v>Claude QA Automation</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>25 Jun 2026</v>
       </c>
       <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
         <v>Not Run</v>
-      </c>
-      <c r="O6" t="str">
-        <v>reports/screenshots/TC-DASH-011-failure.png</v>
       </c>
       <c r="P6" t="str">
         <v/>

--- a/Test Execution Report/Feature Reports/Dashboard.xlsx
+++ b/Test Execution Report/Feature Reports/Dashboard.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O56"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="45.83203125" customWidth="1"/>
@@ -464,16 +464,2711 @@
         <v>Remarks</v>
       </c>
     </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>TC-TICKET-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>TC-TICKET-001 | Create Ticket page loads with all required fields</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K2" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M2" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N2" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>TC-TICKET-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>TC-TICKET-002 | Submit ticket with all required fields filled</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K3" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M3" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N3" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>TC-TICKET-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>TC-TICKET-003 | Project dropdown shows all available projects</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K4" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M4" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N4" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>TC-TICKET-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>TC-TICKET-004 | Selecting project unlocks Platform dropdown</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G5" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K5" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M5" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N5" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>TC-TICKET-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>TC-TICKET-005 | All Ticket Type chips are visible</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K6" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M6" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N6" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>TC-TICKET-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>TC-TICKET-006 | Description character counter updates on input</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G7" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K7" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M7" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N7" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>TC-TICKET-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>TC-TICKET-007 | Reset button clears all filled fields</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G8" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K8" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M8" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N8" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>TC-TICKET-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>TC-TICKET-008 | Page/Screen Name field is optional</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G9" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K9" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M9" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N9" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>TC-TICKET-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>TC-TICKET-009 | Submit with no fields filled shows validation popup</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G10" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K10" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M10" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N10" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
+        <v>TC-TICKET-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>TC-TICKET-010 | Submit without Project shows Missing Information</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G11" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K11" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M11" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N11" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>TC-TICKET-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>TC-TICKET-011 | Submit without Ticket Type shows validation error</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G12" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K12" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M12" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N12" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
+        <v>TC-TICKET-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>TC-TICKET-012 | Submit without Description shows validation error</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G13" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K13" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M13" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N13" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>TC-TICKET-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>TC-TICKET-013 | Submit without Platform shows validation error</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G14" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K14" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M14" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N14" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>TC-TICKET-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>TC-TICKET-014 | Description with exactly 14 chars fails validation</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G15" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K15" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M15" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N15" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>TC-TICKET-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>TC-TICKET-015 | Description with exactly 15 chars passes validation</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G16" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K16" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M16" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N16" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>TC-TICKET-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>TC-TICKET-016 | Description at 2000 chars (max) is accepted</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G17" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M17" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N17" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>TC-TICKET-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>TC-TICKET-017 | Platform chips show all expected options after project selected</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G18" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M18" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N18" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>TC-TICKET-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>TC-TICKET-018 | SQL injection in description is handled safely</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E19" t="str">
+        <v>High</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G19" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M19" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N19" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>TC-TICKET-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>TC-TICKET-019 | XSS payload in description is handled safely</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E20" t="str">
+        <v>High</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G20" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M20" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N20" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>TC-TICKET-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>TC-TICKET-020 | Unauthenticated user is redirected to login page</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E21" t="str">
+        <v>High</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G21" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M21" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N21" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>TC-DASH-001</v>
+      </c>
+      <c r="B22" t="str">
+        <v>TC-DASH-001 | Dashboard page loads with title and H1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G22" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M22" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N22" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>TC-DASH-002</v>
+      </c>
+      <c r="B23" t="str">
+        <v>TC-DASH-002 | All 4 stat cards visible with values</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G23" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+      <c r="K23" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M23" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N23" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>TC-DASH-003</v>
+      </c>
+      <c r="B24" t="str">
+        <v>TC-DASH-003 | OVERVIEW and ANALYTICS buttons visible</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G24" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K24" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M24" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N24" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>TC-DASH-004</v>
+      </c>
+      <c r="B25" t="str">
+        <v>TC-DASH-004 | ANALYTICS tab shows analytics content</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G25" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+      <c r="K25" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M25" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N25" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>TC-DASH-005</v>
+      </c>
+      <c r="B26" t="str">
+        <v>TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G26" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+      <c r="K26" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M26" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N26" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>TC-DASH-006</v>
+      </c>
+      <c r="B27" t="str">
+        <v>TC-DASH-006 | Date range filter applies correctly</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G27" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J27" t="str">
+        <v>_x001b_[31mTest timeout of 30000ms exceeded._x001b_[39m</v>
+      </c>
+      <c r="K27" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M27" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N27" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>TC-DASH-007</v>
+      </c>
+      <c r="B28" t="str">
+        <v>TC-DASH-007 | Reset button clears date filter</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G28" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J28" t="str">
+        <v>_x001b_[31mTest timeout of 30000ms exceeded._x001b_[39m</v>
+      </c>
+      <c r="K28" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M28" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N28" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>TC-DASH-008</v>
+      </c>
+      <c r="B29" t="str">
+        <v>TC-DASH-008 | Invalid date range To &lt; From handled gracefully</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E29" t="str">
+        <v>High</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G29" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J29" t="str">
+        <v>_x001b_[31mTest timeout of 30000ms exceeded._x001b_[39m</v>
+      </c>
+      <c r="K29" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M29" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N29" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>TC-DASH-009</v>
+      </c>
+      <c r="B30" t="str">
+        <v>TC-DASH-009 | Active Tickets table with correct columns</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G30" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K30" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M30" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N30" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
+        <v>TC-DASH-010</v>
+      </c>
+      <c r="B31" t="str">
+        <v>TC-DASH-010 | View All link navigates to ticket list</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G31" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K31" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M31" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N31" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
+        <v>TC-DASH-011</v>
+      </c>
+      <c r="B32" t="str">
+        <v>TC-DASH-011 | All sidebar navigation links present</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G32" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout:  5000ms  Cal</v>
+      </c>
+      <c r="K32" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M32" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N32" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>TC-DASH-012</v>
+      </c>
+      <c r="B33" t="str">
+        <v>TC-DASH-012 | Action Queue badge shows ticket count</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G33" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+      <c r="K33" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M33" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N33" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>TC-DASH-013</v>
+      </c>
+      <c r="B34" t="str">
+        <v>TC-DASH-013 | Search box accepts input</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G34" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K34" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M34" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N34" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>TC-DASH-014</v>
+      </c>
+      <c r="B35" t="str">
+        <v>TC-DASH-014 | User profile dropdown shows username and links</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G35" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K35" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M35" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N35" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>TC-DASH-015</v>
+      </c>
+      <c r="B36" t="str">
+        <v>TC-DASH-015 | Dashboard inaccessible without login</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G36" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K36" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M36" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N36" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>TC-LOGIN-001</v>
+      </c>
+      <c r="B37" t="str">
+        <v>TC-LOGIN-001 | Valid login redirects to dashboard</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G37" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K37" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M37" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N37" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>TC-LOGIN-002</v>
+      </c>
+      <c r="B38" t="str">
+        <v>TC-LOGIN-002 | Login page loads with all required fields</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G38" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M38" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N38" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
+        <v>TC-LOGIN-003</v>
+      </c>
+      <c r="B39" t="str">
+        <v>TC-LOGIN-003 | Password field is masked by default</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G39" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M39" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N39" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
+        <v>TC-LOGIN-004</v>
+      </c>
+      <c r="B40" t="str">
+        <v>TC-LOGIN-004 | Password show/hide toggle works</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G40" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K40" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M40" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N40" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
+        <v>TC-LOGIN-005</v>
+      </c>
+      <c r="B41" t="str">
+        <v>TC-LOGIN-005 | Remember Me checkbox toggles correctly</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G41" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M41" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N41" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
+        <v>TC-LOGIN-006</v>
+      </c>
+      <c r="B42" t="str">
+        <v>TC-LOGIN-006 | Invalid credentials shows error message</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E42" t="str">
+        <v>High</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G42" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M42" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N42" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>TC-LOGIN-007</v>
+      </c>
+      <c r="B43" t="str">
+        <v>TC-LOGIN-007 | Empty username and password blocked</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E43" t="str">
+        <v>High</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G43" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K43" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M43" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N43" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
+        <v>TC-LOGIN-008</v>
+      </c>
+      <c r="B44" t="str">
+        <v>TC-LOGIN-008 | Valid username with empty password blocked</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E44" t="str">
+        <v>High</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G44" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K44" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M44" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N44" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
+        <v>TC-LOGIN-009</v>
+      </c>
+      <c r="B45" t="str">
+        <v>TC-LOGIN-009 | Empty username with valid password blocked</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E45" t="str">
+        <v>High</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G45" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I45" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J45" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K45" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M45" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N45" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
+        <v>TC-LOGIN-010</v>
+      </c>
+      <c r="B46" t="str">
+        <v>TC-LOGIN-010 | Wrong username with correct password rejected</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E46" t="str">
+        <v>High</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G46" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I46" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J46" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K46" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M46" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N46" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str">
+        <v>TC-LOGIN-011</v>
+      </c>
+      <c r="B47" t="str">
+        <v>TC-LOGIN-011 | Correct username with wrong password rejected</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E47" t="str">
+        <v>High</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G47" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J47" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K47" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M47" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N47" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
+        <v>TC-LOGIN-012</v>
+      </c>
+      <c r="B48" t="str">
+        <v>TC-LOGIN-012 | Username with 256 characters handled gracefully</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G48" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K48" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M48" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N48" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str">
+        <v>TC-LOGIN-013</v>
+      </c>
+      <c r="B49" t="str">
+        <v>TC-LOGIN-013 | Password with 256 characters handled gracefully</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G49" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K49" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L49" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M49" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N49" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str">
+        <v>TC-LOGIN-014</v>
+      </c>
+      <c r="B50" t="str">
+        <v>TC-LOGIN-014 | Whitespace-only username is rejected</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G50" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K50" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L50" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M50" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N50" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51" t="str">
+        <v>TC-LOGIN-015</v>
+      </c>
+      <c r="B51" t="str">
+        <v>TC-LOGIN-015 | Special characters in username handled safely</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G51" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K51" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L51" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M51" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N51" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52" xml:space="preserve">
+      <c r="A52" t="str">
+        <v>TC-LOGIN-016</v>
+      </c>
+      <c r="B52" t="str">
+        <v>TC-LOGIN-016 | SQL injection in username handled safely</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E52" t="str">
+        <v>High</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G52" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K52" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L52" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M52" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N52" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53" xml:space="preserve">
+      <c r="A53" t="str">
+        <v>TC-LOGIN-017</v>
+      </c>
+      <c r="B53" t="str">
+        <v>TC-LOGIN-017 | SQL injection in password handled safely</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E53" t="str">
+        <v>High</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G53" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I53" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K53" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L53" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M53" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N53" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54" xml:space="preserve">
+      <c r="A54" t="str">
+        <v>TC-LOGIN-018</v>
+      </c>
+      <c r="B54" t="str">
+        <v>TC-LOGIN-018 | XSS payload in username handled safely</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E54" t="str">
+        <v>High</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G54" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I54" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J54" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K54" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L54" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M54" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N54" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55" xml:space="preserve">
+      <c r="A55" t="str">
+        <v>TC-LOGIN-019</v>
+      </c>
+      <c r="B55" t="str">
+        <v>TC-LOGIN-019 | Unauthenticated access redirects to login</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E55" t="str">
+        <v>High</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G55" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I55" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J55" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K55" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L55" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M55" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N55" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56" xml:space="preserve">
+      <c r="A56" t="str">
+        <v>TC-LOGIN-020</v>
+      </c>
+      <c r="B56" t="str">
+        <v>TC-LOGIN-020 | Username login is case-insensitive (behaviour confirmed)</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online</v>
+      </c>
+      <c r="G56" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to page
+2. Perform action
+3. Verify result</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Refer to test-data/dashboardData.js</v>
+      </c>
+      <c r="I56" t="str">
+        <v>Test should pass per acceptance criteria</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Test passed successfully</v>
+      </c>
+      <c r="K56" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="L56" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M56" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N56" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O56"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P6"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -543,9 +3238,269 @@
         <v>Remarks</v>
       </c>
     </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>BUG-DASHBOARD-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>[FAIL] TC-DASH-002 | All 4 stat cards visible with values</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D2" t="str">
+        <v>TC-DASH-002</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F2" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G2" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to feature page
+2. Execute test steps
+3. Observe failure</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Test should pass successfully</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+      <c r="K2" t="str">
+        <v>New</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M2" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>BUG-DASHBOARD-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>[FAIL] TC-DASH-004 | ANALYTICS tab shows analytics content</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D3" t="str">
+        <v>TC-DASH-004</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F3" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G3" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to feature page
+2. Execute test steps
+3. Observe failure</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Test should pass successfully</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+      <c r="K3" t="str">
+        <v>New</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M3" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>BUG-DASHBOARD-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>[FAIL] TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D4" t="str">
+        <v>TC-DASH-005</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F4" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G4" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="H4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to feature page
+2. Execute test steps
+3. Observe failure</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Test should pass successfully</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+      <c r="K4" t="str">
+        <v>New</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M4" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>BUG-DASHBOARD-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>[FAIL] TC-DASH-011 | All sidebar navigation links present</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D5" t="str">
+        <v>TC-DASH-011</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F5" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G5" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="H5" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to feature page
+2. Execute test steps
+3. Observe failure</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Test should pass successfully</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoBeVisible_x001b_[2m(_x001b_[22m_x001b_[2m)_x001b_[22m failed  Locator:  locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout:  5000ms  Cal</v>
+      </c>
+      <c r="K5" t="str">
+        <v>New</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M5" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>BUG-DASHBOARD-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>[FAIL] TC-DASH-012 | Action Queue badge shows ticket count</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D6" t="str">
+        <v>TC-DASH-012</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F6" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G6" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
+      </c>
+      <c r="H6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to feature page
+2. Execute test steps
+3. Observe failure</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Test should pass successfully</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m  Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+      <c r="K6" t="str">
+        <v>New</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Claude QA Automation</v>
+      </c>
+      <c r="M6" t="str">
+        <v>25 Jun 2026</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Test Execution Report/Feature Reports/Dashboard.xlsx
+++ b/Test Execution Report/Feature Reports/Dashboard.xlsx
@@ -504,13 +504,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M2" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N2" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -553,13 +553,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M3" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N3" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -602,13 +602,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M4" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N4" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -651,13 +651,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M5" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N5" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O5" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -700,13 +700,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M6" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N6" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O6" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -749,13 +749,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M7" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N7" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O7" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
@@ -798,13 +798,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M8" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N8" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O8" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
@@ -847,13 +847,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M9" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N9" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O9" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -896,13 +896,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M10" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N10" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O10" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
@@ -945,13 +945,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M11" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N11" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O11" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="12" xml:space="preserve">
@@ -994,13 +994,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M12" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N12" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O12" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="13" xml:space="preserve">
@@ -1043,13 +1043,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M13" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N13" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O13" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
@@ -1092,13 +1092,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M14" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N14" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O14" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="15" xml:space="preserve">
@@ -1141,13 +1141,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M15" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N15" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O15" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
@@ -1190,13 +1190,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M16" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N16" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O16" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="17" xml:space="preserve">
@@ -1239,13 +1239,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M17" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N17" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O17" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="18" xml:space="preserve">
@@ -1288,13 +1288,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M18" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N18" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O18" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="19" xml:space="preserve">
@@ -1337,13 +1337,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M19" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N19" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O19" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="20" xml:space="preserve">
@@ -1386,13 +1386,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M20" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N20" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O20" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="21" xml:space="preserve">
@@ -1435,13 +1435,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M21" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N21" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O21" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="22" xml:space="preserve">
@@ -1484,13 +1484,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M22" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N22" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O22" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="23" xml:space="preserve">
@@ -1533,13 +1533,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M23" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N23" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O23" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="24" xml:space="preserve">
@@ -1582,13 +1582,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M24" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N24" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O24" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="25" xml:space="preserve">
@@ -1631,13 +1631,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M25" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N25" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O25" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="26" xml:space="preserve">
@@ -1680,13 +1680,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M26" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N26" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O26" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="27" xml:space="preserve">
@@ -1729,13 +1729,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M27" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N27" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O27" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="28" xml:space="preserve">
@@ -1778,13 +1778,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M28" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N28" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O28" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
@@ -1827,13 +1827,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M29" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N29" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O29" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="30" xml:space="preserve">
@@ -1876,13 +1876,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M30" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N30" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O30" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="31" xml:space="preserve">
@@ -1925,13 +1925,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M31" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N31" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O31" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="32" xml:space="preserve">
@@ -1974,13 +1974,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M32" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N32" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O32" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="33" xml:space="preserve">
@@ -2023,13 +2023,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M33" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N33" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O33" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="34" xml:space="preserve">
@@ -2072,13 +2072,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M34" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N34" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O34" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="35" xml:space="preserve">
@@ -2121,13 +2121,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M35" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N35" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O35" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="36" xml:space="preserve">
@@ -2170,13 +2170,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M36" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N36" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O36" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="37" xml:space="preserve">
@@ -2219,13 +2219,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M37" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N37" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O37" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="38" xml:space="preserve">
@@ -2268,13 +2268,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M38" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N38" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O38" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="39" xml:space="preserve">
@@ -2317,13 +2317,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M39" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N39" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O39" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="40" xml:space="preserve">
@@ -2366,13 +2366,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M40" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N40" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O40" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="41" xml:space="preserve">
@@ -2415,13 +2415,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M41" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N41" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O41" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="42" xml:space="preserve">
@@ -2464,13 +2464,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M42" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N42" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O42" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="43" xml:space="preserve">
@@ -2513,13 +2513,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M43" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N43" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O43" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="44" xml:space="preserve">
@@ -2562,13 +2562,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M44" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N44" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O44" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="45" xml:space="preserve">
@@ -2611,13 +2611,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M45" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N45" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O45" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="46" xml:space="preserve">
@@ -2660,13 +2660,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M46" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N46" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O46" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="47" xml:space="preserve">
@@ -2709,13 +2709,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M47" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N47" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O47" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="48" xml:space="preserve">
@@ -2758,13 +2758,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M48" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N48" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O48" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="49" xml:space="preserve">
@@ -2807,13 +2807,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M49" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N49" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O49" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="50" xml:space="preserve">
@@ -2856,13 +2856,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M50" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N50" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O50" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="51" xml:space="preserve">
@@ -2905,13 +2905,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M51" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N51" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O51" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="52" xml:space="preserve">
@@ -2954,13 +2954,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M52" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N52" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O52" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="53" xml:space="preserve">
@@ -3003,13 +3003,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M53" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N53" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O53" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="54" xml:space="preserve">
@@ -3052,13 +3052,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M54" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N54" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O54" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="55" xml:space="preserve">
@@ -3101,13 +3101,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M55" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N55" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O55" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
     <row r="56" xml:space="preserve">
@@ -3150,13 +3150,13 @@
         <v>Claude QA Automation</v>
       </c>
       <c r="M56" t="str">
-        <v>25 Jun 2026</v>
+        <v>26 Jun 2026</v>
       </c>
       <c r="N56" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows</v>
       </c>
       <c r="O56" t="str">
-        <v/>
+        <v>Regression run — 6/26/2026, 2:26:43 AM</v>
       </c>
     </row>
   </sheetData>

--- a/Test Execution Report/Feature Reports/Dashboard.xlsx
+++ b/Test Execution Report/Feature Reports/Dashboard.xlsx
@@ -398,23 +398,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P56"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="45.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
-    <col min="7" max="7" width="42.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
-    <col min="9" max="9" width="38.83203125" customWidth="1"/>
-    <col min="10" max="10" width="45.83203125" customWidth="1"/>
-    <col min="11" max="11" width="8.83203125" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="42.83203125" customWidth="1"/>
-    <col min="15" max="15" width="28.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
+    <col min="7" max="7" width="28.83203125" customWidth="1"/>
+    <col min="8" max="8" width="36.83203125" customWidth="1"/>
+    <col min="9" max="9" width="28.83203125" customWidth="1"/>
+    <col min="10" max="10" width="38.83203125" customWidth="1"/>
+    <col min="11" max="11" width="44.83203125" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" customWidth="1"/>
+    <col min="13" max="13" width="22.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="40.83203125" customWidth="1"/>
+    <col min="16" max="16" width="28.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,59 +435,2812 @@
         <v>Priority</v>
       </c>
       <c r="F1" t="str">
+        <v>Layer</v>
+      </c>
+      <c r="G1" t="str">
         <v>Preconditions</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Test Steps</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Test Data</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Expected Result</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Actual Result</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Status</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Executed By</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>Execution Date</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Environment</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>Remarks</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>TC-TICKET-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>TC-TICKET-001 | Create Ticket page loads with all required fields</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H2" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I2" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Error: expect(page).toHaveTitle(expected) failed Expected pattern: /Create Ticket/i Received string: "Sign In" Timeout: 5000ms Call log: - Expect "toHaveTitle" with timeout 5000ms 14 × unexpected value "Sign In"</v>
+      </c>
+      <c r="L2" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N2" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O2" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TC-TICKET-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>TC-TICKET-002 | Submit ticket with all required fields filled</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F3" t="str">
+        <v>API</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H3" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I3" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L3" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N3" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O3" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>TC-TICKET-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>TC-TICKET-003 | Project dropdown shows all available projects</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F4" t="str">
+        <v>API</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H4" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I4" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L4" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N4" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O4" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TC-TICKET-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>TC-TICKET-004 | Selecting project unlocks Platform dropdown</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F5" t="str">
+        <v>API</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H5" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I5" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L5" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N5" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O5" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TC-TICKET-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>TC-TICKET-005 | All Ticket Type chips are visible</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H6" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I6" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#typeChips .ct-type-chip').filter({ hasText: 'New' }).first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#typeChips .ct-type-chip').filter({ ha</v>
+      </c>
+      <c r="L6" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N6" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O6" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>TC-TICKET-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>TC-TICKET-006 | Description character counter updates on input</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F7" t="str">
+        <v>API</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H7" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I7" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L7" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N7" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O7" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>TC-TICKET-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>TC-TICKET-007 | Reset button clears all filled fields</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F8" t="str">
+        <v>API</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H8" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I8" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L8" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N8" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O8" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>TC-TICKET-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>TC-TICKET-008 | Page/Screen Name field is optional</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F9" t="str">
+        <v>API</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H9" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I9" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L9" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N9" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O9" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>TC-TICKET-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>TC-TICKET-009 | Submit with no fields filled shows validation popup</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F10" t="str">
+        <v>API</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H10" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I10" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L10" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N10" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O10" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>TC-TICKET-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>TC-TICKET-010 | Submit without Project shows Missing Information</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F11" t="str">
+        <v>API</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H11" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I11" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L11" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N11" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O11" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>TC-TICKET-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>TC-TICKET-011 | Submit without Ticket Type shows validation error</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F12" t="str">
+        <v>API</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H12" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I12" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L12" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N12" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O12" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>TC-TICKET-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>TC-TICKET-012 | Submit without Description shows validation error</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F13" t="str">
+        <v>API</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H13" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I13" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L13" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N13" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O13" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>TC-TICKET-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>TC-TICKET-013 | Submit without Platform shows validation error</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F14" t="str">
+        <v>API</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H14" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I14" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L14" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N14" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O14" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TC-TICKET-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>TC-TICKET-014 | Description with exactly 14 chars fails validation</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F15" t="str">
+        <v>API</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H15" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I15" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L15" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N15" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O15" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>TC-TICKET-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>TC-TICKET-015 | Description with exactly 15 chars passes validation</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F16" t="str">
+        <v>API</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H16" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I16" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L16" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N16" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O16" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>TC-TICKET-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>TC-TICKET-016 | Description at 2000 chars (max) is accepted</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F17" t="str">
+        <v>API</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H17" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I17" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L17" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N17" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O17" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>TC-TICKET-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>TC-TICKET-017 | Platform chips show all expected options after project selected</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F18" t="str">
+        <v>API</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H18" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I18" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L18" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N18" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O18" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>TC-TICKET-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>TC-TICKET-018 | SQL injection in description is handled safely</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E19" t="str">
+        <v>High</v>
+      </c>
+      <c r="F19" t="str">
+        <v>API</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H19" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I19" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L19" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N19" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O19" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TC-TICKET-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>TC-TICKET-019 | XSS payload in description is handled safely</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E20" t="str">
+        <v>High</v>
+      </c>
+      <c r="F20" t="str">
+        <v>API</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H20" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I20" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L20" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N20" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O20" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>TC-TICKET-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>TC-TICKET-020 | Unauthenticated user is redirected to login page</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E21" t="str">
+        <v>High</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H21" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I21" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K21" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N21" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O21" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TC-DASH-001</v>
+      </c>
+      <c r="B22" t="str">
+        <v>TC-DASH-001 | Dashboard page loads with title and H1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H22" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I22" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K22" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N22" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O22" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>TC-DASH-002</v>
+      </c>
+      <c r="B23" t="str">
+        <v>TC-DASH-002 | All 4 stat cards visible with values</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H23" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I23" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="L23" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M23" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N23" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O23" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TC-DASH-003</v>
+      </c>
+      <c r="B24" t="str">
+        <v>TC-DASH-003 | OVERVIEW and ANALYTICS buttons visible</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H24" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I24" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#btnOverview') Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#btnOverview')</v>
+      </c>
+      <c r="L24" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N24" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O24" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>TC-DASH-004</v>
+      </c>
+      <c r="B25" t="str">
+        <v>TC-DASH-004 | ANALYTICS tab shows analytics content</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H25" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I25" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="L25" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N25" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O25" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>TC-DASH-005</v>
+      </c>
+      <c r="B26" t="str">
+        <v>TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F26" t="str">
+        <v>API</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H26" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I26" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="L26" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M26" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N26" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O26" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>TC-DASH-006</v>
+      </c>
+      <c r="B27" t="str">
+        <v>TC-DASH-006 | Date range filter applies correctly</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F27" t="str">
+        <v>API</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H27" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I27" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L27" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M27" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N27" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O27" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>TC-DASH-007</v>
+      </c>
+      <c r="B28" t="str">
+        <v>TC-DASH-007 | Reset button clears date filter</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F28" t="str">
+        <v>API</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H28" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I28" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L28" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M28" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N28" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O28" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>TC-DASH-008</v>
+      </c>
+      <c r="B29" t="str">
+        <v>TC-DASH-008 | Invalid date range To &lt; From handled gracefully</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E29" t="str">
+        <v>High</v>
+      </c>
+      <c r="F29" t="str">
+        <v>API</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H29" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I29" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Test timeout of 30000ms exceeded.</v>
+      </c>
+      <c r="L29" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="M29" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N29" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O29" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>TC-DASH-009</v>
+      </c>
+      <c r="B30" t="str">
+        <v>TC-DASH-009 | Active Tickets table with correct columns</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H30" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I30" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('table').first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('table').first()</v>
+      </c>
+      <c r="L30" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M30" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N30" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O30" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>TC-DASH-010</v>
+      </c>
+      <c r="B31" t="str">
+        <v>TC-DASH-010 | View All link navigates to ticket list</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H31" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I31" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K31" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L31" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N31" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O31" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>TC-DASH-011</v>
+      </c>
+      <c r="B32" t="str">
+        <v>TC-DASH-011 | All sidebar navigation links present</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F32" t="str">
+        <v>API</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H32" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I32" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('a[href="/Ticket/Create"]').first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('a[href="/Ticket/Create"]').first()</v>
+      </c>
+      <c r="L32" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M32" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N32" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O32" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>TC-DASH-012</v>
+      </c>
+      <c r="B33" t="str">
+        <v>TC-DASH-012 | Action Queue badge shows ticket count</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H33" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I33" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="L33" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M33" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N33" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O33" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>TC-DASH-013</v>
+      </c>
+      <c r="B34" t="str">
+        <v>TC-DASH-013 | Search box accepts input</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H34" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I34" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('input[placeholder="Search"]').first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('input[placeholder="Search"]').first()</v>
+      </c>
+      <c r="L34" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M34" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N34" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O34" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>TC-DASH-014</v>
+      </c>
+      <c r="B35" t="str">
+        <v>TC-DASH-014 | User profile dropdown shows username and links</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H35" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I35" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K35" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L35" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M35" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N35" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O35" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>TC-DASH-015</v>
+      </c>
+      <c r="B36" t="str">
+        <v>TC-DASH-015 | Dashboard inaccessible without login</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H36" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I36" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K36" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L36" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M36" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N36" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O36" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>TC-LOGIN-001</v>
+      </c>
+      <c r="B37" t="str">
+        <v>TC-LOGIN-001 | Valid login redirects to dashboard</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H37" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I37" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K37" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L37" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M37" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N37" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O37" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>TC-LOGIN-002</v>
+      </c>
+      <c r="B38" t="str">
+        <v>TC-LOGIN-002 | Login page loads with all required fields</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H38" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I38" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K38" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M38" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N38" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O38" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>TC-LOGIN-003</v>
+      </c>
+      <c r="B39" t="str">
+        <v>TC-LOGIN-003 | Password field is masked by default</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H39" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I39" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K39" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M39" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N39" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O39" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>TC-LOGIN-004</v>
+      </c>
+      <c r="B40" t="str">
+        <v>TC-LOGIN-004 | Password show/hide toggle works</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H40" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I40" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K40" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L40" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N40" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O40" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>TC-LOGIN-005</v>
+      </c>
+      <c r="B41" t="str">
+        <v>TC-LOGIN-005 | Remember Me checkbox toggles correctly</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H41" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I41" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K41" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M41" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N41" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O41" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>TC-LOGIN-006</v>
+      </c>
+      <c r="B42" t="str">
+        <v>TC-LOGIN-006 | Invalid credentials shows error message</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E42" t="str">
+        <v>High</v>
+      </c>
+      <c r="F42" t="str">
+        <v>API</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H42" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I42" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K42" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M42" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N42" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O42" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>TC-LOGIN-007</v>
+      </c>
+      <c r="B43" t="str">
+        <v>TC-LOGIN-007 | Empty username and password blocked</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E43" t="str">
+        <v>High</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H43" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I43" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K43" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L43" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M43" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N43" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O43" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>TC-LOGIN-008</v>
+      </c>
+      <c r="B44" t="str">
+        <v>TC-LOGIN-008 | Valid username with empty password blocked</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E44" t="str">
+        <v>High</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H44" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I44" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K44" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L44" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M44" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N44" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O44" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>TC-LOGIN-009</v>
+      </c>
+      <c r="B45" t="str">
+        <v>TC-LOGIN-009 | Empty username with valid password blocked</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E45" t="str">
+        <v>High</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H45" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I45" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J45" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K45" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L45" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M45" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N45" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O45" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>TC-LOGIN-010</v>
+      </c>
+      <c r="B46" t="str">
+        <v>TC-LOGIN-010 | Wrong username with correct password rejected</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E46" t="str">
+        <v>High</v>
+      </c>
+      <c r="F46" t="str">
+        <v>API</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H46" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I46" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J46" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K46" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L46" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M46" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N46" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O46" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>TC-LOGIN-011</v>
+      </c>
+      <c r="B47" t="str">
+        <v>TC-LOGIN-011 | Correct username with wrong password rejected</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E47" t="str">
+        <v>High</v>
+      </c>
+      <c r="F47" t="str">
+        <v>API</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H47" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I47" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J47" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K47" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L47" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M47" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N47" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O47" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>TC-LOGIN-012</v>
+      </c>
+      <c r="B48" t="str">
+        <v>TC-LOGIN-012 | Username with 256 characters handled gracefully</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F48" t="str">
+        <v>API</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H48" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I48" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K48" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L48" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M48" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N48" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O48" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>TC-LOGIN-013</v>
+      </c>
+      <c r="B49" t="str">
+        <v>TC-LOGIN-013 | Password with 256 characters handled gracefully</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F49" t="str">
+        <v>API</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H49" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I49" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K49" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L49" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M49" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N49" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O49" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>TC-LOGIN-014</v>
+      </c>
+      <c r="B50" t="str">
+        <v>TC-LOGIN-014 | Whitespace-only username is rejected</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H50" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I50" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K50" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L50" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M50" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N50" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O50" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>TC-LOGIN-015</v>
+      </c>
+      <c r="B51" t="str">
+        <v>TC-LOGIN-015 | Special characters in username handled safely</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F51" t="str">
+        <v>API</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H51" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I51" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K51" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L51" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M51" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N51" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O51" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>TC-LOGIN-016</v>
+      </c>
+      <c r="B52" t="str">
+        <v>TC-LOGIN-016 | SQL injection in username handled safely</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E52" t="str">
+        <v>High</v>
+      </c>
+      <c r="F52" t="str">
+        <v>API</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H52" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I52" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K52" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L52" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M52" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N52" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O52" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>TC-LOGIN-017</v>
+      </c>
+      <c r="B53" t="str">
+        <v>TC-LOGIN-017 | SQL injection in password handled safely</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E53" t="str">
+        <v>High</v>
+      </c>
+      <c r="F53" t="str">
+        <v>API</v>
+      </c>
+      <c r="G53" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H53" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I53" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K53" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L53" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M53" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N53" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O53" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>TC-LOGIN-018</v>
+      </c>
+      <c r="B54" t="str">
+        <v>TC-LOGIN-018 | XSS payload in username handled safely</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E54" t="str">
+        <v>High</v>
+      </c>
+      <c r="F54" t="str">
+        <v>API</v>
+      </c>
+      <c r="G54" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H54" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I54" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J54" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K54" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L54" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M54" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N54" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O54" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>TC-LOGIN-019</v>
+      </c>
+      <c r="B55" t="str">
+        <v>TC-LOGIN-019 | Unauthenticated access redirects to login</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E55" t="str">
+        <v>High</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G55" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H55" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I55" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J55" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K55" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L55" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M55" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N55" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O55" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>TC-LOGIN-020</v>
+      </c>
+      <c r="B56" t="str">
+        <v>TC-LOGIN-020 | Username login is case-insensitive (behaviour confirmed)</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F56" t="str">
+        <v>API</v>
+      </c>
+      <c r="G56" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H56" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I56" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K56" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L56" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M56" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N56" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O56" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P56" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P56"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P11"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="8.83203125" customWidth="1"/>
-    <col min="7" max="7" width="42.83203125" customWidth="1"/>
+    <col min="7" max="7" width="40.83203125" customWidth="1"/>
     <col min="8" max="8" width="42.83203125" customWidth="1"/>
-    <col min="9" max="9" width="35.83203125" customWidth="1"/>
-    <col min="10" max="10" width="45.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+    <col min="9" max="9" width="36.83203125" customWidth="1"/>
+    <col min="10" max="10" width="46.83203125" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="12" max="12" width="22.83203125" customWidth="1"/>
     <col min="13" max="13" width="14.83203125" customWidth="1"/>
     <col min="14" max="14" width="12.83203125" customWidth="1"/>
     <col min="15" max="15" width="16.83203125" customWidth="1"/>
@@ -543,9 +3297,519 @@
         <v>Remarks</v>
       </c>
     </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>BUG-DASHBOARD-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>[FAIL] TC-TICKET-001 | Create Ticket page loads with all required fields</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D2" t="str">
+        <v>TC-TICKET-001</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F2" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G2" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-TICKET-001</v>
+      </c>
+      <c r="I2" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Error: expect(page).toHaveTitle(expected) failed Expected pattern: /Create Ticket/i Received string: "Sign In" Timeout: 5000ms Call log: - Expect "toHaveTitle" with timeout 5000ms 14 × unexpected value "Sign In"</v>
+      </c>
+      <c r="K2" t="str">
+        <v>New</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M2" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>BUG-DASHBOARD-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>[FAIL] TC-TICKET-005 | All Ticket Type chips are visible</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D3" t="str">
+        <v>TC-TICKET-005</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F3" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G3" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-TICKET-005</v>
+      </c>
+      <c r="I3" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#typeChips .ct-type-chip').filter({ hasText: 'New' }).first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#typeChips .ct-type-chip').filter({ ha</v>
+      </c>
+      <c r="K3" t="str">
+        <v>New</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M3" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>BUG-DASHBOARD-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>[FAIL] TC-DASH-002 | All 4 stat cards visible with values</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D4" t="str">
+        <v>TC-DASH-002</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F4" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G4" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H4" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-002</v>
+      </c>
+      <c r="I4" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K4" t="str">
+        <v>New</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M4" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>BUG-DASHBOARD-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>[FAIL] TC-DASH-003 | OVERVIEW and ANALYTICS buttons visible</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D5" t="str">
+        <v>TC-DASH-003</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F5" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G5" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H5" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-003</v>
+      </c>
+      <c r="I5" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#btnOverview') Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#btnOverview')</v>
+      </c>
+      <c r="K5" t="str">
+        <v>New</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M5" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>BUG-DASHBOARD-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>[FAIL] TC-DASH-004 | ANALYTICS tab shows analytics content</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D6" t="str">
+        <v>TC-DASH-004</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F6" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G6" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H6" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-004</v>
+      </c>
+      <c r="I6" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K6" t="str">
+        <v>New</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M6" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>BUG-DASHBOARD-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>[FAIL] TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D7" t="str">
+        <v>TC-DASH-005</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F7" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G7" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H7" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-005</v>
+      </c>
+      <c r="I7" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K7" t="str">
+        <v>New</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M7" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>BUG-DASHBOARD-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>[FAIL] TC-DASH-009 | Active Tickets table with correct columns</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D8" t="str">
+        <v>TC-DASH-009</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F8" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G8" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H8" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-009</v>
+      </c>
+      <c r="I8" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('table').first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('table').first()</v>
+      </c>
+      <c r="K8" t="str">
+        <v>New</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M8" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>BUG-DASHBOARD-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>[FAIL] TC-DASH-011 | All sidebar navigation links present</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D9" t="str">
+        <v>TC-DASH-011</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F9" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G9" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H9" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-011</v>
+      </c>
+      <c r="I9" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('a[href="/Ticket/Create"]').first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('a[href="/Ticket/Create"]').first()</v>
+      </c>
+      <c r="K9" t="str">
+        <v>New</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M9" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>BUG-DASHBOARD-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>[FAIL] TC-DASH-012 | Action Queue badge shows ticket count</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D10" t="str">
+        <v>TC-DASH-012</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F10" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G10" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H10" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-012</v>
+      </c>
+      <c r="I10" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K10" t="str">
+        <v>New</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M10" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
+        <v>BUG-DASHBOARD-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>[FAIL] TC-DASH-013 | Search box accepts input</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D11" t="str">
+        <v>TC-DASH-013</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F11" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G11" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H11" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-013</v>
+      </c>
+      <c r="I11" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('input[placeholder="Search"]').first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('input[placeholder="Search"]').first()</v>
+      </c>
+      <c r="K11" t="str">
+        <v>New</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M11" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Test Execution Report/Feature Reports/Dashboard.xlsx
+++ b/Test Execution Report/Feature Reports/Dashboard.xlsx
@@ -550,10 +550,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K3" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="L3" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M3" t="str">
         <v>Playwright Automation</v>
@@ -600,10 +600,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K4" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="L4" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M4" t="str">
         <v>Playwright Automation</v>
@@ -650,10 +650,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K5" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="L5" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M5" t="str">
         <v>Playwright Automation</v>
@@ -750,10 +750,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K7" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#txtDescription')</v>
       </c>
       <c r="L7" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M7" t="str">
         <v>Playwright Automation</v>
@@ -800,10 +800,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K8" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#txtPageName')</v>
       </c>
       <c r="L8" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M8" t="str">
         <v>Playwright Automation</v>
@@ -850,10 +850,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K9" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="L9" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M9" t="str">
         <v>Playwright Automation</v>
@@ -900,10 +900,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K10" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for getByRole('button', { name: /submit ticket/i })</v>
       </c>
       <c r="L10" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M10" t="str">
         <v>Playwright Automation</v>
@@ -950,10 +950,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K11" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Type..."]')</v>
       </c>
       <c r="L11" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M11" t="str">
         <v>Playwright Automation</v>
@@ -1000,10 +1000,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K12" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="L12" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M12" t="str">
         <v>Playwright Automation</v>
@@ -1050,10 +1050,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K13" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="L13" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M13" t="str">
         <v>Playwright Automation</v>
@@ -1100,10 +1100,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K14" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="L14" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M14" t="str">
         <v>Playwright Automation</v>
@@ -1150,10 +1150,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K15" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="L15" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M15" t="str">
         <v>Playwright Automation</v>
@@ -1200,10 +1200,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K16" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="L16" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M16" t="str">
         <v>Playwright Automation</v>
@@ -1250,10 +1250,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K17" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#txtDescription')</v>
       </c>
       <c r="L17" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M17" t="str">
         <v>Playwright Automation</v>
@@ -1300,10 +1300,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K18" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="L18" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M18" t="str">
         <v>Playwright Automation</v>
@@ -1350,10 +1350,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K19" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="L19" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M19" t="str">
         <v>Playwright Automation</v>
@@ -1400,10 +1400,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K20" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="L20" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M20" t="str">
         <v>Playwright Automation</v>
@@ -1750,10 +1750,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K27" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-26" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
       </c>
       <c r="L27" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M27" t="str">
         <v>Playwright Automation</v>
@@ -1800,10 +1800,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K28" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_apply') - locator resolved to &lt;button id="dr_apply" class="w-full text-[0.75rem] font-bold text-white bg-blue-600 hover:bg-blue-700 rounded py-1.5 transition-colors"&gt;Apply Range&lt;/button&gt; - attempting click ac</v>
       </c>
       <c r="L28" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M28" t="str">
         <v>Playwright Automation</v>
@@ -1850,10 +1850,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K29" t="str">
-        <v>Test timeout of 30000ms exceeded.</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_apply') - locator resolved to &lt;button id="dr_apply" class="w-full text-[0.75rem] font-bold text-white bg-blue-600 hover:bg-blue-700 rounded py-1.5 transition-colors"&gt;Apply Range&lt;/button&gt; - attempting click ac</v>
       </c>
       <c r="L29" t="str">
-        <v>NOT RUN</v>
+        <v>FAIL</v>
       </c>
       <c r="M29" t="str">
         <v>Playwright Automation</v>
@@ -2100,10 +2100,10 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K34" t="str">
-        <v>Error: expect(locator).toBeVisible() failed Locator: locator('input[placeholder="Search"]').first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('input[placeholder="Search"]').first()</v>
+        <v>All assertions passed via Playwright</v>
       </c>
       <c r="L34" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="M34" t="str">
         <v>Playwright Automation</v>
@@ -3227,7 +3227,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P30"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3353,13 +3353,13 @@
         <v>BUG-DASHBOARD-002</v>
       </c>
       <c r="B3" t="str">
-        <v>[FAIL] TC-TICKET-005 | All Ticket Type chips are visible</v>
+        <v>[FAIL] TC-TICKET-002 | Submit ticket with all required fields filled</v>
       </c>
       <c r="C3" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D3" t="str">
-        <v>TC-TICKET-005</v>
+        <v>TC-TICKET-002</v>
       </c>
       <c r="E3" t="str">
         <v>Low</v>
@@ -3372,13 +3372,13 @@
       </c>
       <c r="H3" t="str" xml:space="preserve">
         <v xml:space="preserve">See spec: tests/dashboard.spec.js
-TC: TC-TICKET-005</v>
+TC: TC-TICKET-002</v>
       </c>
       <c r="I3" t="str">
         <v>All Playwright assertions pass</v>
       </c>
       <c r="J3" t="str">
-        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#typeChips .ct-type-chip').filter({ hasText: 'New' }).first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#typeChips .ct-type-chip').filter({ ha</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="K3" t="str">
         <v>New</v>
@@ -3404,13 +3404,13 @@
         <v>BUG-DASHBOARD-003</v>
       </c>
       <c r="B4" t="str">
-        <v>[FAIL] TC-DASH-002 | All 4 stat cards visible with values</v>
+        <v>[FAIL] TC-TICKET-003 | Project dropdown shows all available projects</v>
       </c>
       <c r="C4" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D4" t="str">
-        <v>TC-DASH-002</v>
+        <v>TC-TICKET-003</v>
       </c>
       <c r="E4" t="str">
         <v>Low</v>
@@ -3423,13 +3423,13 @@
       </c>
       <c r="H4" t="str" xml:space="preserve">
         <v xml:space="preserve">See spec: tests/dashboard.spec.js
-TC: TC-DASH-002</v>
+TC: TC-TICKET-003</v>
       </c>
       <c r="I4" t="str">
         <v>All Playwright assertions pass</v>
       </c>
       <c r="J4" t="str">
-        <v>Error: expect(received).toBeTruthy() Received: false</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="K4" t="str">
         <v>New</v>
@@ -3455,13 +3455,13 @@
         <v>BUG-DASHBOARD-004</v>
       </c>
       <c r="B5" t="str">
-        <v>[FAIL] TC-DASH-003 | OVERVIEW and ANALYTICS buttons visible</v>
+        <v>[FAIL] TC-TICKET-004 | Selecting project unlocks Platform dropdown</v>
       </c>
       <c r="C5" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D5" t="str">
-        <v>TC-DASH-003</v>
+        <v>TC-TICKET-004</v>
       </c>
       <c r="E5" t="str">
         <v>Low</v>
@@ -3474,13 +3474,13 @@
       </c>
       <c r="H5" t="str" xml:space="preserve">
         <v xml:space="preserve">See spec: tests/dashboard.spec.js
-TC: TC-DASH-003</v>
+TC: TC-TICKET-004</v>
       </c>
       <c r="I5" t="str">
         <v>All Playwright assertions pass</v>
       </c>
       <c r="J5" t="str">
-        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#btnOverview') Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#btnOverview')</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="K5" t="str">
         <v>New</v>
@@ -3506,13 +3506,13 @@
         <v>BUG-DASHBOARD-005</v>
       </c>
       <c r="B6" t="str">
-        <v>[FAIL] TC-DASH-004 | ANALYTICS tab shows analytics content</v>
+        <v>[FAIL] TC-TICKET-005 | All Ticket Type chips are visible</v>
       </c>
       <c r="C6" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D6" t="str">
-        <v>TC-DASH-004</v>
+        <v>TC-TICKET-005</v>
       </c>
       <c r="E6" t="str">
         <v>Low</v>
@@ -3525,13 +3525,13 @@
       </c>
       <c r="H6" t="str" xml:space="preserve">
         <v xml:space="preserve">See spec: tests/dashboard.spec.js
-TC: TC-DASH-004</v>
+TC: TC-TICKET-005</v>
       </c>
       <c r="I6" t="str">
         <v>All Playwright assertions pass</v>
       </c>
       <c r="J6" t="str">
-        <v>Error: expect(received).toBeTruthy() Received: false</v>
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#typeChips .ct-type-chip').filter({ hasText: 'New' }).first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#typeChips .ct-type-chip').filter({ ha</v>
       </c>
       <c r="K6" t="str">
         <v>New</v>
@@ -3557,13 +3557,13 @@
         <v>BUG-DASHBOARD-006</v>
       </c>
       <c r="B7" t="str">
-        <v>[FAIL] TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
+        <v>[FAIL] TC-TICKET-006 | Description character counter updates on input</v>
       </c>
       <c r="C7" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D7" t="str">
-        <v>TC-DASH-005</v>
+        <v>TC-TICKET-006</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
@@ -3576,13 +3576,13 @@
       </c>
       <c r="H7" t="str" xml:space="preserve">
         <v xml:space="preserve">See spec: tests/dashboard.spec.js
-TC: TC-DASH-005</v>
+TC: TC-TICKET-006</v>
       </c>
       <c r="I7" t="str">
         <v>All Playwright assertions pass</v>
       </c>
       <c r="J7" t="str">
-        <v>Error: expect(received).toBeTruthy() Received: false</v>
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#txtDescription')</v>
       </c>
       <c r="K7" t="str">
         <v>New</v>
@@ -3608,13 +3608,13 @@
         <v>BUG-DASHBOARD-007</v>
       </c>
       <c r="B8" t="str">
-        <v>[FAIL] TC-DASH-009 | Active Tickets table with correct columns</v>
+        <v>[FAIL] TC-TICKET-007 | Reset button clears all filled fields</v>
       </c>
       <c r="C8" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D8" t="str">
-        <v>TC-DASH-009</v>
+        <v>TC-TICKET-007</v>
       </c>
       <c r="E8" t="str">
         <v>Low</v>
@@ -3627,13 +3627,13 @@
       </c>
       <c r="H8" t="str" xml:space="preserve">
         <v xml:space="preserve">See spec: tests/dashboard.spec.js
-TC: TC-DASH-009</v>
+TC: TC-TICKET-007</v>
       </c>
       <c r="I8" t="str">
         <v>All Playwright assertions pass</v>
       </c>
       <c r="J8" t="str">
-        <v>Error: expect(locator).toBeVisible() failed Locator: locator('table').first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('table').first()</v>
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#txtPageName')</v>
       </c>
       <c r="K8" t="str">
         <v>New</v>
@@ -3659,13 +3659,13 @@
         <v>BUG-DASHBOARD-008</v>
       </c>
       <c r="B9" t="str">
-        <v>[FAIL] TC-DASH-011 | All sidebar navigation links present</v>
+        <v>[FAIL] TC-TICKET-008 | Page/Screen Name field is optional</v>
       </c>
       <c r="C9" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D9" t="str">
-        <v>TC-DASH-011</v>
+        <v>TC-TICKET-008</v>
       </c>
       <c r="E9" t="str">
         <v>Low</v>
@@ -3678,13 +3678,13 @@
       </c>
       <c r="H9" t="str" xml:space="preserve">
         <v xml:space="preserve">See spec: tests/dashboard.spec.js
-TC: TC-DASH-011</v>
+TC: TC-TICKET-008</v>
       </c>
       <c r="I9" t="str">
         <v>All Playwright assertions pass</v>
       </c>
       <c r="J9" t="str">
-        <v>Error: expect(locator).toBeVisible() failed Locator: locator('a[href="/Ticket/Create"]').first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('a[href="/Ticket/Create"]').first()</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
       </c>
       <c r="K9" t="str">
         <v>New</v>
@@ -3710,13 +3710,13 @@
         <v>BUG-DASHBOARD-009</v>
       </c>
       <c r="B10" t="str">
-        <v>[FAIL] TC-DASH-012 | Action Queue badge shows ticket count</v>
+        <v>[FAIL] TC-TICKET-009 | Submit with no fields filled shows validation popup</v>
       </c>
       <c r="C10" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D10" t="str">
-        <v>TC-DASH-012</v>
+        <v>TC-TICKET-009</v>
       </c>
       <c r="E10" t="str">
         <v>Low</v>
@@ -3729,13 +3729,13 @@
       </c>
       <c r="H10" t="str" xml:space="preserve">
         <v xml:space="preserve">See spec: tests/dashboard.spec.js
-TC: TC-DASH-012</v>
+TC: TC-TICKET-009</v>
       </c>
       <c r="I10" t="str">
         <v>All Playwright assertions pass</v>
       </c>
       <c r="J10" t="str">
-        <v>Error: expect(received).toBeTruthy() Received: false</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for getByRole('button', { name: /submit ticket/i })</v>
       </c>
       <c r="K10" t="str">
         <v>New</v>
@@ -3761,13 +3761,13 @@
         <v>BUG-DASHBOARD-010</v>
       </c>
       <c r="B11" t="str">
-        <v>[FAIL] TC-DASH-013 | Search box accepts input</v>
+        <v>[FAIL] TC-TICKET-010 | Submit without Project shows Missing Information</v>
       </c>
       <c r="C11" t="str">
         <v>Dashboard</v>
       </c>
       <c r="D11" t="str">
-        <v>TC-DASH-013</v>
+        <v>TC-TICKET-010</v>
       </c>
       <c r="E11" t="str">
         <v>Low</v>
@@ -3780,13 +3780,13 @@
       </c>
       <c r="H11" t="str" xml:space="preserve">
         <v xml:space="preserve">See spec: tests/dashboard.spec.js
-TC: TC-DASH-013</v>
+TC: TC-TICKET-010</v>
       </c>
       <c r="I11" t="str">
         <v>All Playwright assertions pass</v>
       </c>
       <c r="J11" t="str">
-        <v>Error: expect(locator).toBeVisible() failed Locator: locator('input[placeholder="Search"]').first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('input[placeholder="Search"]').first()</v>
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Type..."]')</v>
       </c>
       <c r="K11" t="str">
         <v>New</v>
@@ -3807,9 +3807,978 @@
         <v/>
       </c>
     </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>BUG-DASHBOARD-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>[FAIL] TC-TICKET-011 | Submit without Ticket Type shows validation error</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D12" t="str">
+        <v>TC-TICKET-011</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F12" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G12" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H12" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-TICKET-011</v>
+      </c>
+      <c r="I12" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J12" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
+      </c>
+      <c r="K12" t="str">
+        <v>New</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M12" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
+        <v>BUG-DASHBOARD-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>[FAIL] TC-TICKET-012 | Submit without Description shows validation error</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D13" t="str">
+        <v>TC-TICKET-012</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F13" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G13" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H13" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-TICKET-012</v>
+      </c>
+      <c r="I13" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J13" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
+      </c>
+      <c r="K13" t="str">
+        <v>New</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M13" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>BUG-DASHBOARD-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>[FAIL] TC-TICKET-013 | Submit without Platform shows validation error</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D14" t="str">
+        <v>TC-TICKET-013</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F14" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G14" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H14" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-TICKET-013</v>
+      </c>
+      <c r="I14" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J14" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
+      </c>
+      <c r="K14" t="str">
+        <v>New</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M14" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>BUG-DASHBOARD-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>[FAIL] TC-TICKET-014 | Description with exactly 14 chars fails validation</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D15" t="str">
+        <v>TC-TICKET-014</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F15" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G15" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H15" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-TICKET-014</v>
+      </c>
+      <c r="I15" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J15" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
+      </c>
+      <c r="K15" t="str">
+        <v>New</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M15" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>BUG-DASHBOARD-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>[FAIL] TC-TICKET-015 | Description with exactly 15 chars passes validation</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D16" t="str">
+        <v>TC-TICKET-015</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F16" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G16" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H16" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-TICKET-015</v>
+      </c>
+      <c r="I16" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J16" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
+      </c>
+      <c r="K16" t="str">
+        <v>New</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M16" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>BUG-DASHBOARD-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>[FAIL] TC-TICKET-016 | Description at 2000 chars (max) is accepted</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D17" t="str">
+        <v>TC-TICKET-016</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F17" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G17" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H17" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-TICKET-016</v>
+      </c>
+      <c r="I17" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J17" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#txtDescription')</v>
+      </c>
+      <c r="K17" t="str">
+        <v>New</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M17" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>BUG-DASHBOARD-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>[FAIL] TC-TICKET-017 | Platform chips show all expected options after project selected</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D18" t="str">
+        <v>TC-TICKET-017</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F18" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G18" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H18" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-TICKET-017</v>
+      </c>
+      <c r="I18" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J18" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
+      </c>
+      <c r="K18" t="str">
+        <v>New</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M18" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>BUG-DASHBOARD-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>[FAIL] TC-TICKET-018 | SQL injection in description is handled safely</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D19" t="str">
+        <v>TC-TICKET-018</v>
+      </c>
+      <c r="E19" t="str">
+        <v>High</v>
+      </c>
+      <c r="F19" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G19" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H19" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-TICKET-018</v>
+      </c>
+      <c r="I19" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J19" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
+      </c>
+      <c r="K19" t="str">
+        <v>New</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M19" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>BUG-DASHBOARD-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>[FAIL] TC-TICKET-019 | XSS payload in description is handled safely</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D20" t="str">
+        <v>TC-TICKET-019</v>
+      </c>
+      <c r="E20" t="str">
+        <v>High</v>
+      </c>
+      <c r="F20" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G20" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H20" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-TICKET-019</v>
+      </c>
+      <c r="I20" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J20" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('input[placeholder="Select Project..."]')</v>
+      </c>
+      <c r="K20" t="str">
+        <v>New</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M20" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>BUG-DASHBOARD-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>[FAIL] TC-DASH-002 | All 4 stat cards visible with values</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D21" t="str">
+        <v>TC-DASH-002</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F21" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G21" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H21" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-002</v>
+      </c>
+      <c r="I21" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K21" t="str">
+        <v>New</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M21" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>BUG-DASHBOARD-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>[FAIL] TC-DASH-003 | OVERVIEW and ANALYTICS buttons visible</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D22" t="str">
+        <v>TC-DASH-003</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F22" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G22" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H22" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-003</v>
+      </c>
+      <c r="I22" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#btnOverview') Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#btnOverview')</v>
+      </c>
+      <c r="K22" t="str">
+        <v>New</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M22" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>BUG-DASHBOARD-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>[FAIL] TC-DASH-004 | ANALYTICS tab shows analytics content</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D23" t="str">
+        <v>TC-DASH-004</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F23" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G23" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H23" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-004</v>
+      </c>
+      <c r="I23" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K23" t="str">
+        <v>New</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M23" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>BUG-DASHBOARD-023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>[FAIL] TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D24" t="str">
+        <v>TC-DASH-005</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F24" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G24" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H24" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-005</v>
+      </c>
+      <c r="I24" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K24" t="str">
+        <v>New</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M24" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>BUG-DASHBOARD-024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>[FAIL] TC-DASH-006 | Date range filter applies correctly</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D25" t="str">
+        <v>TC-DASH-006</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F25" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G25" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H25" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-006</v>
+      </c>
+      <c r="I25" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J25" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-26" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="K25" t="str">
+        <v>New</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M25" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>BUG-DASHBOARD-025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>[FAIL] TC-DASH-007 | Reset button clears date filter</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D26" t="str">
+        <v>TC-DASH-007</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F26" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G26" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H26" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-007</v>
+      </c>
+      <c r="I26" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J26" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_apply') - locator resolved to &lt;button id="dr_apply" class="w-full text-[0.75rem] font-bold text-white bg-blue-600 hover:bg-blue-700 rounded py-1.5 transition-colors"&gt;Apply Range&lt;/button&gt; - attempting click ac</v>
+      </c>
+      <c r="K26" t="str">
+        <v>New</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M26" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>BUG-DASHBOARD-026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>[FAIL] TC-DASH-008 | Invalid date range To &lt; From handled gracefully</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D27" t="str">
+        <v>TC-DASH-008</v>
+      </c>
+      <c r="E27" t="str">
+        <v>High</v>
+      </c>
+      <c r="F27" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G27" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H27" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-008</v>
+      </c>
+      <c r="I27" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J27" t="str">
+        <v>TimeoutError: locator.click: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_apply') - locator resolved to &lt;button id="dr_apply" class="w-full text-[0.75rem] font-bold text-white bg-blue-600 hover:bg-blue-700 rounded py-1.5 transition-colors"&gt;Apply Range&lt;/button&gt; - attempting click ac</v>
+      </c>
+      <c r="K27" t="str">
+        <v>New</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M27" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>BUG-DASHBOARD-027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>[FAIL] TC-DASH-009 | Active Tickets table with correct columns</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D28" t="str">
+        <v>TC-DASH-009</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F28" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G28" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H28" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-009</v>
+      </c>
+      <c r="I28" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('table').first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('table').first()</v>
+      </c>
+      <c r="K28" t="str">
+        <v>New</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M28" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>BUG-DASHBOARD-028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>[FAIL] TC-DASH-011 | All sidebar navigation links present</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D29" t="str">
+        <v>TC-DASH-011</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F29" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G29" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H29" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-011</v>
+      </c>
+      <c r="I29" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('a[href="/Ticket/Create"]').first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('a[href="/Ticket/Create"]').first()</v>
+      </c>
+      <c r="K29" t="str">
+        <v>New</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M29" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>BUG-DASHBOARD-029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>[FAIL] TC-DASH-012 | Action Queue badge shows ticket count</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D30" t="str">
+        <v>TC-DASH-012</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F30" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G30" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H30" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-012</v>
+      </c>
+      <c r="I30" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K30" t="str">
+        <v>New</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M30" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P30"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Test Execution Report/Feature Reports/Dashboard.xlsx
+++ b/Test Execution Report/Feature Reports/Dashboard.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P58"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="45.83203125" customWidth="1"/>
@@ -468,16 +468,2866 @@
         <v>Remarks</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>TC-TICKET-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>TC-TICKET-001 | Create Ticket page loads with all required fields</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H2" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I2" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K2" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L2" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N2" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O2" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TC-TICKET-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>TC-TICKET-002 | Project dropdown shows all available projects</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F3" t="str">
+        <v>API</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H3" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I3" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K3" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L3" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N3" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O3" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>TC-TICKET-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>TC-TICKET-003 | All 6 Ticket Type chips are visible</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H4" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I4" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K4" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L4" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N4" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O4" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TC-TICKET-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>TC-TICKET-004 | All 6 platform chips visible on page load</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H5" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I5" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#platformChips .ct-type-chip').filter({ hasText: 'Backend' }).first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#platformChips .ct-type-chip')</v>
+      </c>
+      <c r="L5" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N5" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O5" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TC-TICKET-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>TC-TICKET-005 | Description character counter updates on input</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F6" t="str">
+        <v>API</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H6" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I6" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K6" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L6" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N6" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O6" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>TC-TICKET-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>TC-TICKET-006 | File attachment — PNG upload accepted</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F7" t="str">
+        <v>API</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H7" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I7" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Error: ENOENT: no such file or directory, stat 'C:\Users\Turbosoft PC\OneDrive\Pictures\Screenshots 1\Screenshot 2026-06-26 091258.png'</v>
+      </c>
+      <c r="L7" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N7" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O7" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>TC-TICKET-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>TC-TICKET-007 | Reset button clears all filled fields</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F8" t="str">
+        <v>API</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H8" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I8" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K8" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L8" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N8" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O8" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>TC-TICKET-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>TC-TICKET-008 | Submit with no fields filled shows Missing Information</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F9" t="str">
+        <v>API</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H9" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I9" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K9" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L9" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N9" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O9" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>TC-TICKET-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>TC-TICKET-009 | Submit without Project shows validation error</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F10" t="str">
+        <v>API</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H10" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I10" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K10" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L10" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N10" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O10" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>TC-TICKET-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>TC-TICKET-010 | Submit without Ticket Type shows validation error</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F11" t="str">
+        <v>API</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H11" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I11" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K11" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L11" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N11" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O11" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>TC-TICKET-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>TC-TICKET-011 | Submit without Description shows validation error</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F12" t="str">
+        <v>API</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H12" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I12" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K12" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L12" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N12" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O12" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>TC-TICKET-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>TC-TICKET-012 | Submit with description under 15 chars blocked</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F13" t="str">
+        <v>API</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H13" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I13" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K13" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L13" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N13" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O13" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>TC-TICKET-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>TC-TICKET-013 | Page/Screen Name field is optional</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F14" t="str">
+        <v>API</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H14" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I14" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K14" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L14" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N14" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O14" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TC-TICKET-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>TC-TICKET-014 | Description with exactly 15 chars passes validation</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F15" t="str">
+        <v>API</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H15" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I15" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K15" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L15" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N15" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O15" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>TC-TICKET-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>TC-TICKET-015 | Description at 2000 chars accepted by counter</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F16" t="str">
+        <v>API</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H16" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I16" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K16" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L16" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N16" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O16" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>TC-TICKET-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>TC-TICKET-016 | Description over 2000 chars truncated to max</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F17" t="str">
+        <v>API</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H17" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I17" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K17" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N17" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O17" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>TC-TICKET-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>TC-TICKET-017 | Long page name (300 chars) handled gracefully</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F18" t="str">
+        <v>API</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H18" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I18" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K18" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N18" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O18" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>TC-TICKET-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>TC-TICKET-018 | Special characters in description handled safely</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F19" t="str">
+        <v>API</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H19" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I19" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K19" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N19" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O19" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TC-TICKET-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>TC-TICKET-019 | SQL injection in description handled safely</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E20" t="str">
+        <v>High</v>
+      </c>
+      <c r="F20" t="str">
+        <v>API</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H20" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I20" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K20" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N20" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O20" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>TC-TICKET-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>TC-TICKET-020 | XSS payload in description handled safely</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E21" t="str">
+        <v>High</v>
+      </c>
+      <c r="F21" t="str">
+        <v>API</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H21" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I21" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K21" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N21" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O21" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TC-TICKET-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>TC-TICKET-021 | Unauthenticated access redirected to login</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E22" t="str">
+        <v>High</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H22" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I22" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Error: expect(page).toHaveURL(expected) failed Expected pattern: /Login|Account/i Received string: "http://customerportal.dev-ts.online/Ticket/Create" Timeout: 5000ms Call log: - Expect "toHaveURL" with timeout 5000ms 14 × unexpected value "http://customerportal.dev-ts.online/Ticket/Create"</v>
+      </c>
+      <c r="L22" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N22" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O22" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>TC-TICKET-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>TC-TICKET-022 | HTML injection in description handled safely</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F23" t="str">
+        <v>API</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H23" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I23" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K23" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L23" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M23" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N23" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O23" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TC-DASH-001</v>
+      </c>
+      <c r="B24" t="str">
+        <v>TC-DASH-001 | Dashboard page loads with title and H1</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H24" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I24" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K24" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L24" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N24" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O24" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>TC-DASH-002</v>
+      </c>
+      <c r="B25" t="str">
+        <v>TC-DASH-002 | All 4 stat cards visible with values</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H25" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I25" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="L25" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N25" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O25" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>TC-DASH-003</v>
+      </c>
+      <c r="B26" t="str">
+        <v>TC-DASH-003 | OVERVIEW and ANALYTICS buttons visible</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H26" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I26" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K26" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L26" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M26" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N26" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O26" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>TC-DASH-004</v>
+      </c>
+      <c r="B27" t="str">
+        <v>TC-DASH-004 | ANALYTICS tab shows analytics content</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H27" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I27" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="L27" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M27" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N27" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O27" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>TC-DASH-005</v>
+      </c>
+      <c r="B28" t="str">
+        <v>TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F28" t="str">
+        <v>API</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H28" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I28" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="L28" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M28" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N28" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O28" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>TC-DASH-006</v>
+      </c>
+      <c r="B29" t="str">
+        <v>TC-DASH-006 | Date range filter applies correctly</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F29" t="str">
+        <v>API</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H29" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I29" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K29" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-26" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="L29" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M29" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N29" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O29" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>TC-DASH-007</v>
+      </c>
+      <c r="B30" t="str">
+        <v>TC-DASH-007 | Reset button clears date filter</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F30" t="str">
+        <v>API</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H30" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I30" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K30" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-26" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="L30" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M30" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N30" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O30" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>TC-DASH-008</v>
+      </c>
+      <c r="B31" t="str">
+        <v>TC-DASH-008 | Invalid date range To &lt; From handled gracefully</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E31" t="str">
+        <v>High</v>
+      </c>
+      <c r="F31" t="str">
+        <v>API</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H31" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I31" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K31" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-26" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="L31" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N31" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O31" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>TC-DASH-009</v>
+      </c>
+      <c r="B32" t="str">
+        <v>TC-DASH-009 | Active Tickets table with correct columns</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H32" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I32" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K32" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L32" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M32" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N32" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O32" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>TC-DASH-010</v>
+      </c>
+      <c r="B33" t="str">
+        <v>TC-DASH-010 | View All link navigates to ticket list</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H33" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I33" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K33" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L33" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M33" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N33" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O33" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>TC-DASH-011</v>
+      </c>
+      <c r="B34" t="str">
+        <v>TC-DASH-011 | All sidebar navigation links present</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F34" t="str">
+        <v>API</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H34" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I34" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout: 5000ms Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('a[href="/Ticket/Index"]').first() 13 × locator resolved to &lt;a data-id="4" tab</v>
+      </c>
+      <c r="L34" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M34" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N34" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O34" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>TC-DASH-012</v>
+      </c>
+      <c r="B35" t="str">
+        <v>TC-DASH-012 | Action Queue badge shows ticket count</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H35" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I35" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K35" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L35" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M35" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N35" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O35" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>TC-DASH-013</v>
+      </c>
+      <c r="B36" t="str">
+        <v>TC-DASH-013 | Search box accepts input</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H36" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I36" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K36" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L36" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M36" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N36" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O36" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>TC-DASH-014</v>
+      </c>
+      <c r="B37" t="str">
+        <v>TC-DASH-014 | User profile dropdown shows username and links</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H37" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I37" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K37" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L37" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M37" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N37" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O37" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>TC-DASH-015</v>
+      </c>
+      <c r="B38" t="str">
+        <v>TC-DASH-015 | Dashboard inaccessible without login</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H38" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I38" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K38" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M38" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N38" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O38" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>TC-LOGIN-001</v>
+      </c>
+      <c r="B39" t="str">
+        <v>TC-LOGIN-001 | Valid login redirects to dashboard</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H39" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I39" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K39" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M39" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N39" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O39" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>TC-LOGIN-002</v>
+      </c>
+      <c r="B40" t="str">
+        <v>TC-LOGIN-002 | Login page loads with all required fields</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H40" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I40" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K40" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L40" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N40" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O40" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>TC-LOGIN-003</v>
+      </c>
+      <c r="B41" t="str">
+        <v>TC-LOGIN-003 | Password field is masked by default</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H41" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I41" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K41" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M41" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N41" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O41" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>TC-LOGIN-004</v>
+      </c>
+      <c r="B42" t="str">
+        <v>TC-LOGIN-004 | Password show/hide toggle works</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H42" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I42" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K42" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M42" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N42" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O42" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>TC-LOGIN-005</v>
+      </c>
+      <c r="B43" t="str">
+        <v>TC-LOGIN-005 | Remember Me checkbox toggles correctly</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Positive</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H43" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I43" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K43" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L43" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M43" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N43" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O43" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>TC-LOGIN-006</v>
+      </c>
+      <c r="B44" t="str">
+        <v>TC-LOGIN-006 | Invalid credentials shows error message</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E44" t="str">
+        <v>High</v>
+      </c>
+      <c r="F44" t="str">
+        <v>API</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H44" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I44" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K44" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L44" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M44" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N44" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O44" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>TC-LOGIN-007</v>
+      </c>
+      <c r="B45" t="str">
+        <v>TC-LOGIN-007 | Empty username and password blocked</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E45" t="str">
+        <v>High</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H45" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I45" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J45" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K45" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L45" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M45" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N45" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O45" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>TC-LOGIN-008</v>
+      </c>
+      <c r="B46" t="str">
+        <v>TC-LOGIN-008 | Valid username with empty password blocked</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E46" t="str">
+        <v>High</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H46" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I46" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J46" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K46" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L46" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M46" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N46" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O46" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>TC-LOGIN-009</v>
+      </c>
+      <c r="B47" t="str">
+        <v>TC-LOGIN-009 | Empty username with valid password blocked</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E47" t="str">
+        <v>High</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H47" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I47" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J47" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K47" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L47" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M47" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N47" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O47" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>TC-LOGIN-010</v>
+      </c>
+      <c r="B48" t="str">
+        <v>TC-LOGIN-010 | Wrong username with correct password rejected</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E48" t="str">
+        <v>High</v>
+      </c>
+      <c r="F48" t="str">
+        <v>API</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H48" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I48" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K48" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L48" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M48" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N48" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O48" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>TC-LOGIN-011</v>
+      </c>
+      <c r="B49" t="str">
+        <v>TC-LOGIN-011 | Correct username with wrong password rejected</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="E49" t="str">
+        <v>High</v>
+      </c>
+      <c r="F49" t="str">
+        <v>API</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H49" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I49" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K49" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L49" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M49" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N49" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O49" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>TC-LOGIN-012</v>
+      </c>
+      <c r="B50" t="str">
+        <v>TC-LOGIN-012 | Username with 256 characters handled gracefully</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F50" t="str">
+        <v>API</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H50" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I50" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K50" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L50" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M50" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N50" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O50" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>TC-LOGIN-013</v>
+      </c>
+      <c r="B51" t="str">
+        <v>TC-LOGIN-013 | Password with 256 characters handled gracefully</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F51" t="str">
+        <v>API</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H51" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I51" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K51" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L51" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M51" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N51" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O51" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>TC-LOGIN-014</v>
+      </c>
+      <c r="B52" t="str">
+        <v>TC-LOGIN-014 | Whitespace-only username is rejected</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H52" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I52" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K52" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L52" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M52" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N52" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O52" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>TC-LOGIN-015</v>
+      </c>
+      <c r="B53" t="str">
+        <v>TC-LOGIN-015 | Special characters in username handled safely</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F53" t="str">
+        <v>API</v>
+      </c>
+      <c r="G53" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H53" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I53" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K53" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L53" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M53" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N53" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O53" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>TC-LOGIN-016</v>
+      </c>
+      <c r="B54" t="str">
+        <v>TC-LOGIN-016 | SQL injection in username handled safely</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E54" t="str">
+        <v>High</v>
+      </c>
+      <c r="F54" t="str">
+        <v>API</v>
+      </c>
+      <c r="G54" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H54" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I54" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J54" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Error: expect(page).toHaveURL(expected) failed Expected pattern: /Login/ Received string: "" Timeout: 5000ms Call log: - Expect "toHaveURL" with timeout 5000ms - waiting for navigation to finish...</v>
+      </c>
+      <c r="L54" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="M54" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N54" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O54" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>TC-LOGIN-017</v>
+      </c>
+      <c r="B55" t="str">
+        <v>TC-LOGIN-017 | SQL injection in password handled safely</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E55" t="str">
+        <v>High</v>
+      </c>
+      <c r="F55" t="str">
+        <v>API</v>
+      </c>
+      <c r="G55" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H55" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I55" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J55" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K55" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L55" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M55" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N55" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O55" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>TC-LOGIN-018</v>
+      </c>
+      <c r="B56" t="str">
+        <v>TC-LOGIN-018 | XSS payload in username handled safely</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E56" t="str">
+        <v>High</v>
+      </c>
+      <c r="F56" t="str">
+        <v>API</v>
+      </c>
+      <c r="G56" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H56" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I56" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K56" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L56" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M56" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N56" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O56" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>TC-LOGIN-019</v>
+      </c>
+      <c r="B57" t="str">
+        <v>TC-LOGIN-019 | Unauthenticated access redirects to login</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Security</v>
+      </c>
+      <c r="E57" t="str">
+        <v>High</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Auto</v>
+      </c>
+      <c r="G57" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H57" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I57" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J57" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K57" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L57" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M57" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N57" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O57" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>TC-LOGIN-020</v>
+      </c>
+      <c r="B58" t="str">
+        <v>TC-LOGIN-020 | Username login is case-insensitive (behaviour confirmed)</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F58" t="str">
+        <v>API</v>
+      </c>
+      <c r="G58" t="str">
+        <v>Application accessible at http://customerportal.dev-ts.online; user sajith_xyz active</v>
+      </c>
+      <c r="H58" t="str">
+        <v>(See Playwright spec: tests/dashboard.spec.js)</v>
+      </c>
+      <c r="I58" t="str">
+        <v>See test-data/dashboardData.js</v>
+      </c>
+      <c r="J58" t="str">
+        <v>Test assertions pass per spec definition</v>
+      </c>
+      <c r="K58" t="str">
+        <v>All assertions passed via Playwright</v>
+      </c>
+      <c r="L58" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M58" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="N58" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="O58" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P58"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P12"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -547,9 +3397,570 @@
         <v>Remarks</v>
       </c>
     </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>BUG-DASHBOARD-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>[FAIL] TC-TICKET-004 | All 6 platform chips visible on page load</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D2" t="str">
+        <v>TC-TICKET-004</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F2" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G2" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-TICKET-004</v>
+      </c>
+      <c r="I2" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('#platformChips .ct-type-chip').filter({ hasText: 'Backend' }).first() Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('#platformChips .ct-type-chip')</v>
+      </c>
+      <c r="K2" t="str">
+        <v>New</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M2" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>BUG-DASHBOARD-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>[FAIL] TC-TICKET-006 | File attachment — PNG upload accepted</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D3" t="str">
+        <v>TC-TICKET-006</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F3" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G3" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-TICKET-006</v>
+      </c>
+      <c r="I3" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Error: ENOENT: no such file or directory, stat 'C:\Users\Turbosoft PC\OneDrive\Pictures\Screenshots 1\Screenshot 2026-06-26 091258.png'</v>
+      </c>
+      <c r="K3" t="str">
+        <v>New</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M3" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>BUG-DASHBOARD-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>[FAIL] TC-TICKET-021 | Unauthenticated access redirected to login</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D4" t="str">
+        <v>TC-TICKET-021</v>
+      </c>
+      <c r="E4" t="str">
+        <v>High</v>
+      </c>
+      <c r="F4" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G4" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H4" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-TICKET-021</v>
+      </c>
+      <c r="I4" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Error: expect(page).toHaveURL(expected) failed Expected pattern: /Login|Account/i Received string: "http://customerportal.dev-ts.online/Ticket/Create" Timeout: 5000ms Call log: - Expect "toHaveURL" with timeout 5000ms 14 × unexpected value "http://customerportal.dev-ts.online/Ticket/Create"</v>
+      </c>
+      <c r="K4" t="str">
+        <v>New</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M4" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>BUG-DASHBOARD-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>[FAIL] TC-DASH-002 | All 4 stat cards visible with values</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D5" t="str">
+        <v>TC-DASH-002</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F5" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G5" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H5" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-002</v>
+      </c>
+      <c r="I5" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K5" t="str">
+        <v>New</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M5" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>BUG-DASHBOARD-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>[FAIL] TC-DASH-004 | ANALYTICS tab shows analytics content</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D6" t="str">
+        <v>TC-DASH-004</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F6" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G6" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H6" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-004</v>
+      </c>
+      <c r="I6" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K6" t="str">
+        <v>New</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M6" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>BUG-DASHBOARD-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>[FAIL] TC-DASH-005 | Switch back to OVERVIEW from ANALYTICS</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D7" t="str">
+        <v>TC-DASH-005</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F7" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G7" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H7" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-005</v>
+      </c>
+      <c r="I7" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Error: expect(received).toBeTruthy() Received: false</v>
+      </c>
+      <c r="K7" t="str">
+        <v>New</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M7" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>BUG-DASHBOARD-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>[FAIL] TC-DASH-006 | Date range filter applies correctly</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D8" t="str">
+        <v>TC-DASH-006</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F8" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G8" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H8" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-006</v>
+      </c>
+      <c r="I8" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J8" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-26" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="K8" t="str">
+        <v>New</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M8" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>BUG-DASHBOARD-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>[FAIL] TC-DASH-007 | Reset button clears date filter</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D9" t="str">
+        <v>TC-DASH-007</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F9" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G9" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H9" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-007</v>
+      </c>
+      <c r="I9" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J9" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-26" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="K9" t="str">
+        <v>New</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M9" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>BUG-DASHBOARD-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>[FAIL] TC-DASH-008 | Invalid date range To &lt; From handled gracefully</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D10" t="str">
+        <v>TC-DASH-008</v>
+      </c>
+      <c r="E10" t="str">
+        <v>High</v>
+      </c>
+      <c r="F10" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G10" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H10" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-008</v>
+      </c>
+      <c r="I10" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J10" t="str">
+        <v>TimeoutError: locator.fill: Timeout 15000ms exceeded. Call log: - waiting for locator('#dr_from') - locator resolved to &lt;input type="date" id="dr_from" max="2026-06-26" class="w-full text-[0.75rem] py-1.5 px-2 border border-gray-200 rounded mb-2 dark:bg-[#1a1a2e] dark:border-[#2b2b40] dark:text-gray</v>
+      </c>
+      <c r="K10" t="str">
+        <v>New</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M10" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
+        <v>BUG-DASHBOARD-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>[FAIL] TC-DASH-011 | All sidebar navigation links present</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D11" t="str">
+        <v>TC-DASH-011</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F11" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G11" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H11" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-DASH-011</v>
+      </c>
+      <c r="I11" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Error: expect(locator).toBeVisible() failed Locator: locator('a[href="/Ticket/Index"]').first() Expected: visible Received: hidden Timeout: 5000ms Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('a[href="/Ticket/Index"]').first() 13 × locator resolved to &lt;a data-id="4" tab</v>
+      </c>
+      <c r="K11" t="str">
+        <v>New</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M11" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>BUG-DASHBOARD-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>[FAIL] TC-LOGIN-016 | SQL injection in username handled safely</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D12" t="str">
+        <v>TC-LOGIN-016</v>
+      </c>
+      <c r="E12" t="str">
+        <v>High</v>
+      </c>
+      <c r="F12" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G12" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H12" t="str" xml:space="preserve">
+        <v xml:space="preserve">See spec: tests/dashboard.spec.js
+TC: TC-LOGIN-016</v>
+      </c>
+      <c r="I12" t="str">
+        <v>All Playwright assertions pass</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Error: expect(page).toHaveURL(expected) failed Expected pattern: /Login/ Received string: "" Timeout: 5000ms Call log: - Expect "toHaveURL" with timeout 5000ms - waiting for navigation to finish...</v>
+      </c>
+      <c r="K12" t="str">
+        <v>New</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M12" t="str">
+        <v>26 Jun 2026</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P12"/>
   </ignoredErrors>
 </worksheet>
 </file>